--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843EEF6D-6D56-4659-9EBF-94661E9A6119}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723E973C-CDD4-4127-A868-8EB1E54025E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="calculating_COD" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$3:$AK$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$3:$AJ$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +58,7 @@
     <author>tc={59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{C7B782E2-F656-DB45-97AC-D2B1A4310A43}">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{C7B782E2-F656-DB45-97AC-D2B1A4310A43}">
       <text>
         <r>
           <rPr>
@@ -93,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE3" authorId="0" shapeId="0" xr:uid="{C3505123-F90F-DE41-BEE8-86A5DB659096}">
+    <comment ref="AD3" authorId="0" shapeId="0" xr:uid="{C3505123-F90F-DE41-BEE8-86A5DB659096}">
       <text>
         <r>
           <rPr>
@@ -126,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{BC23984A-4BE5-DB42-8CB2-421621628373}">
+    <comment ref="J4" authorId="1" shapeId="0" xr:uid="{BC23984A-4BE5-DB42-8CB2-421621628373}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W4" authorId="2" shapeId="0" xr:uid="{A973AB73-A4B2-DB42-8CE2-2E9D2BA6D327}">
+    <comment ref="V4" authorId="2" shapeId="0" xr:uid="{A973AB73-A4B2-DB42-8CE2-2E9D2BA6D327}">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA4" authorId="3" shapeId="0" xr:uid="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
+    <comment ref="Z4" authorId="3" shapeId="0" xr:uid="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
       <text>
         <r>
           <rPr>
@@ -315,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF4" authorId="4" shapeId="0" xr:uid="{D83D8722-287D-8543-91DC-DFD968583D4B}">
+    <comment ref="AE4" authorId="4" shapeId="0" xr:uid="{D83D8722-287D-8543-91DC-DFD968583D4B}">
       <text>
         <r>
           <rPr>
@@ -332,7 +332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K5" authorId="5" shapeId="0" xr:uid="{4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}">
+    <comment ref="J5" authorId="5" shapeId="0" xr:uid="{4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}">
       <text>
         <r>
           <rPr>
@@ -349,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="6" shapeId="0" xr:uid="{8B1BECD1-664B-894E-902F-58308D659DA9}">
+    <comment ref="V5" authorId="6" shapeId="0" xr:uid="{8B1BECD1-664B-894E-902F-58308D659DA9}">
       <text>
         <r>
           <rPr>
@@ -412,7 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA5" authorId="7" shapeId="0" xr:uid="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
+    <comment ref="Z5" authorId="7" shapeId="0" xr:uid="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
       <text>
         <r>
           <rPr>
@@ -429,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF5" authorId="8" shapeId="0" xr:uid="{009AF6C5-B9AC-7541-9E56-015D22C54F6F}">
+    <comment ref="AE5" authorId="8" shapeId="0" xr:uid="{009AF6C5-B9AC-7541-9E56-015D22C54F6F}">
       <text>
         <r>
           <rPr>
@@ -446,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="9" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
+    <comment ref="J6" authorId="9" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
       <text>
         <r>
           <rPr>
@@ -463,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W6" authorId="10" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
+    <comment ref="V6" authorId="10" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA6" authorId="11" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
+    <comment ref="Z6" authorId="11" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
       <text>
         <r>
           <rPr>
@@ -543,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF6" authorId="12" shapeId="0" xr:uid="{B40E02FA-A395-684A-865E-E43D81BF9EF7}">
+    <comment ref="AE6" authorId="12" shapeId="0" xr:uid="{B40E02FA-A395-684A-865E-E43D81BF9EF7}">
       <text>
         <r>
           <rPr>
@@ -560,7 +560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="13" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
+    <comment ref="J7" authorId="13" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
       <text>
         <r>
           <rPr>
@@ -577,7 +577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W7" authorId="14" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
+    <comment ref="V7" authorId="14" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
       <text>
         <r>
           <rPr>
@@ -594,7 +594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA7" authorId="15" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
+    <comment ref="Z7" authorId="15" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
       <text>
         <r>
           <rPr>
@@ -611,7 +611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF7" authorId="16" shapeId="0" xr:uid="{507182A8-A16E-3B46-A78B-C475F7E79FFC}">
+    <comment ref="AE7" authorId="16" shapeId="0" xr:uid="{507182A8-A16E-3B46-A78B-C475F7E79FFC}">
       <text>
         <r>
           <rPr>
@@ -628,7 +628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="17" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
+    <comment ref="J8" authorId="17" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
       <text>
         <r>
           <rPr>
@@ -645,7 +645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="18" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
+    <comment ref="V8" authorId="18" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
       <text>
         <r>
           <rPr>
@@ -708,7 +708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA8" authorId="19" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
+    <comment ref="Z8" authorId="19" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
       <text>
         <r>
           <rPr>
@@ -725,7 +725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF8" authorId="20" shapeId="0" xr:uid="{C8D487C4-854D-254E-A24C-BB3F3463062E}">
+    <comment ref="AE8" authorId="20" shapeId="0" xr:uid="{C8D487C4-854D-254E-A24C-BB3F3463062E}">
       <text>
         <r>
           <rPr>
@@ -788,7 +788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="21" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
+    <comment ref="J9" authorId="21" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
       <text>
         <r>
           <rPr>
@@ -805,7 +805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W9" authorId="22" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
+    <comment ref="V9" authorId="22" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
       <text>
         <r>
           <rPr>
@@ -868,7 +868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="23" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
+    <comment ref="Z9" authorId="23" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
       <text>
         <r>
           <rPr>
@@ -885,7 +885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF9" authorId="24" shapeId="0" xr:uid="{59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}">
+    <comment ref="AE9" authorId="24" shapeId="0" xr:uid="{59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}">
       <text>
         <r>
           <rPr>
@@ -948,7 +948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K10" authorId="21" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
+    <comment ref="J10" authorId="21" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
       <text>
         <r>
           <rPr>
@@ -965,7 +965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="22" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
+    <comment ref="V10" authorId="22" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
       <text>
         <r>
           <rPr>
@@ -1028,7 +1028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA10" authorId="23" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
+    <comment ref="Z10" authorId="23" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
       <text>
         <r>
           <rPr>
@@ -1045,7 +1045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF10" authorId="24" shapeId="0" xr:uid="{FD6930BF-6346-42D5-92D3-2FDEDA69C33D}">
+    <comment ref="AE10" authorId="24" shapeId="0" xr:uid="{FD6930BF-6346-42D5-92D3-2FDEDA69C33D}">
       <text>
         <r>
           <rPr>
@@ -1108,7 +1108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="21" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
+    <comment ref="J11" authorId="21" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
       <text>
         <r>
           <rPr>
@@ -1125,7 +1125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W11" authorId="22" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
+    <comment ref="V11" authorId="22" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
       <text>
         <r>
           <rPr>
@@ -1188,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA11" authorId="23" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
+    <comment ref="Z11" authorId="23" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
       <text>
         <r>
           <rPr>
@@ -1205,7 +1205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF11" authorId="24" shapeId="0" xr:uid="{125C2159-6A41-496C-957A-98F84A831963}">
+    <comment ref="AE11" authorId="24" shapeId="0" xr:uid="{125C2159-6A41-496C-957A-98F84A831963}">
       <text>
         <r>
           <rPr>
@@ -1268,7 +1268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="21" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
+    <comment ref="J12" authorId="21" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
       <text>
         <r>
           <rPr>
@@ -1285,7 +1285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="22" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
+    <comment ref="V12" authorId="22" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
       <text>
         <r>
           <rPr>
@@ -1348,7 +1348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA12" authorId="23" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
+    <comment ref="Z12" authorId="23" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
       <text>
         <r>
           <rPr>
@@ -1365,7 +1365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF12" authorId="24" shapeId="0" xr:uid="{A6C2F603-09FF-44E5-B2D4-65A036090CD5}">
+    <comment ref="AE12" authorId="24" shapeId="0" xr:uid="{A6C2F603-09FF-44E5-B2D4-65A036090CD5}">
       <text>
         <r>
           <rPr>
@@ -1428,7 +1428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K13" authorId="21" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
+    <comment ref="J13" authorId="21" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
       <text>
         <r>
           <rPr>
@@ -1445,7 +1445,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W13" authorId="22" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
+    <comment ref="V13" authorId="22" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
       <text>
         <r>
           <rPr>
@@ -1508,7 +1508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA13" authorId="23" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
+    <comment ref="Z13" authorId="23" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
       <text>
         <r>
           <rPr>
@@ -1525,7 +1525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF13" authorId="24" shapeId="0" xr:uid="{B81F7C15-5FA5-4154-852C-1E0CA3F919A7}">
+    <comment ref="AE13" authorId="24" shapeId="0" xr:uid="{B81F7C15-5FA5-4154-852C-1E0CA3F919A7}">
       <text>
         <r>
           <rPr>
@@ -1593,7 +1593,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="197">
   <si>
     <t>variable_parameter</t>
   </si>
@@ -1694,9 +1694,6 @@
     <t>yield_MO</t>
   </si>
   <si>
-    <t>TOC_COD_mol_m2_yr_precipitation</t>
-  </si>
-  <si>
     <t>https://en.wikipedia.org/wiki/Chemical_oxygen_demand</t>
   </si>
   <si>
@@ -1722,9 +1719,6 @@
   </si>
   <si>
     <t>COD [mol O2 per mol substrate]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> this is a rough estimate and therefore is not real-temperature-adjusted at this stage</t>
   </si>
   <si>
     <t>average_precipitation_mm_yr</t>
@@ -2664,9 +2658,6 @@
     <t xml:space="preserve">mol per  m^3 </t>
   </si>
   <si>
-    <t>100% at 12 degrees, between 50 and 100% at 16 degrees, between 0 and50% at 20 degrees (Brielmann 2011). Assuming that half of the fauna population behaves like amphipods and half like asellids, 100% survival at 12 degrees, (75% survival at 16 degrees,) 25 % at 20 degrees. Taking the endpoint 20 degrees, 0.25 of the population survives after an increase by 8 degrees. This means that 0.75 have died. Thus , for each degree of increase, 0.75/8 = 0.09375 , roughly 1 % of the individuals die.    above or below 10 degree</t>
-  </si>
-  <si>
     <t>in Gerritse et al. (1992): 10.6 g- mol-1, i.e. 10.6/12 mol biomass / mol acetate -"Expressed as grams of cell carbon produced per mole of carbon substrate consumed." This was multiplied with 1.07 mol COD / mol biomass and divided by 2 mol COD / mol acetate</t>
   </si>
   <si>
@@ -2691,9 +2682,6 @@
     <t>average precipitation (mm / year). Plesne precipitation, to deal with Kopacek TOC in precipitation. The mean of 1402 and 1437, which are the yearly precipitaiton for Plesne and Certovo respectively (Kopacek et al., 2009: Canopy leaching .. )</t>
   </si>
   <si>
-    <t>the fraction of precipitation recharged to groundwater. Here a very simplified estimate which is not congruent with field measurements and has to be updated in future runs if it proves sensitive. "The infiltration rate in Chinese loess aquifers ranges between 0.19 and 0.34 m/year, representing 6–13% of the annual precipitation." Liu et al. 2024; ca. 8% Seidenfaden et al. 2023</t>
-  </si>
-  <si>
     <t>concentration of total organic carbon (TOC) in precipitation: 208 mmol / m^2 / yr in Plesne, 199 mmol / m^2 / yr in Certovo; i.e. 203.5 on average; J. Kopacek et al. 2008; Kopacek, J., Turek, J., Hejzlar, J., Santruckova, H., 2009. Canopy leaching of nutrients and metals in a mountain spruce forest. Atmospheric Environment 43, 5443–5453. https://doi.org/10.1016/j.atmosenv.2009.07.031</t>
   </si>
   <si>
@@ -2703,9 +2691,6 @@
     <t>rate constant for bacterial uptake and oxidation of acetate Gerritse et al. (1992), assuming COD can be degraded like acetate, which is an error-prone assumption</t>
   </si>
   <si>
-    <t>for now for lack of better values, the same as microbes. Alternatively , one could set 0.1 as in Lindeman, but thats less.This is dry mass.</t>
-  </si>
-  <si>
     <t>excretion rate of fauna; constant rate; excretion is biodegradable organic carbon (BOC) and added to that pool</t>
   </si>
   <si>
@@ -2713,6 +2698,15 @@
   </si>
   <si>
     <t>the factor with which maximum measured biomass of fauna was multiplied to derive carrying capacity of fauna</t>
+  </si>
+  <si>
+    <t>the fraction of precipitation recharged to groundwater.  "The infiltration rate in Chinese loess aquifers ranges between 0.19 and 0.34 m/year, representing 6–13% of the annual precipitation." Liu et al. 2024; ca. 8% Seidenfaden et al. 2023</t>
+  </si>
+  <si>
+    <t>this is a rough estimate and therefore is not real-temperature-adjusted at this stage</t>
+  </si>
+  <si>
+    <t>100% survival at 12 degrees, between 50 and 100% at 16 degrees, between 0 and50% at 20 degrees (Brielmann 2011). Assuming that half of the fauna population behaves like amphipods and half like asellids, 100% survival at 12 degrees, (75% survival at 16 degrees,) 25 % at 20 degrees. Taking the endpoint 20 degrees, 0.25 of the population survives after an increase by 8 degrees. This means that 0.75 have died. Thus , for each degree of increase, 0.75/8 = 0.09375 , roughly 1 % of the individuals die.    above or below 12 degree</t>
   </si>
 </sst>
 </file>
@@ -3381,18 +3375,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.19921875" customWidth="1"/>
-    <col min="14" max="14" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.19921875" customWidth="1"/>
+    <col min="13" max="13" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3400,67 +3394,64 @@
         <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" t="s">
+        <v>181</v>
+      </c>
+      <c r="O1" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>180</v>
+      </c>
+      <c r="W1" t="s">
         <v>190</v>
       </c>
-      <c r="G1" t="s">
+      <c r="X1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>186</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AF1" t="s">
         <v>191</v>
       </c>
-      <c r="H1" t="s">
-        <v>192</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="AH1" t="s">
         <v>193</v>
       </c>
-      <c r="N1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P1" t="s">
-        <v>5</v>
-      </c>
-      <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" t="s">
-        <v>183</v>
-      </c>
-      <c r="V1" t="s">
-        <v>195</v>
-      </c>
-      <c r="X1" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>196</v>
       </c>
-      <c r="AI1" t="s">
-        <v>198</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37">
+    </row>
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3468,46 +3459,46 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" t="s">
-        <v>181</v>
+      <c r="J2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" t="s">
         <v>8</v>
       </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
       <c r="T2" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="U2" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="V2" t="s">
+        <v>183</v>
+      </c>
+      <c r="W2" t="s">
         <v>185</v>
       </c>
-      <c r="W2" t="s">
-        <v>186</v>
-      </c>
-      <c r="X2" t="s">
-        <v>188</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AC2" t="s">
         <v>10</v>
       </c>
+      <c r="AF2" t="s">
+        <v>27</v>
+      </c>
       <c r="AG2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3518,109 +3509,106 @@
         <v>4</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H3" t="s">
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="J3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W3" t="s">
         <v>46</v>
       </c>
-      <c r="L3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>12</v>
-      </c>
-      <c r="R3" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V3" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" t="s">
-        <v>20</v>
-      </c>
-      <c r="X3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y3" s="4" t="s">
+      <c r="X3" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="Y3" t="s">
+        <v>22</v>
+      </c>
       <c r="Z3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="AB3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AC3" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="AI3" t="s">
         <v>54</v>
       </c>
       <c r="AJ3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36">
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -3641,103 +3629,103 @@
         <f t="shared" ref="H4:H13" si="1">203.5/1000</f>
         <v>0.20349999999999999</v>
       </c>
-      <c r="J4">
+      <c r="I4">
         <f>H4/F4*1000</f>
         <v>0.14336033814723495</v>
       </c>
+      <c r="J4">
+        <f>I4*7.5</f>
+        <v>1.0752025361042621</v>
+      </c>
       <c r="K4">
-        <f>J4*7.5</f>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L4">
-        <f>K4/1000</f>
+        <f>J4/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
-      <c r="M4" s="4">
+      <c r="L4" s="4">
         <v>10</v>
       </c>
+      <c r="M4">
+        <f>L4*J4</f>
+        <v>10.752025361042621</v>
+      </c>
       <c r="N4">
-        <f>M4*K4</f>
-        <v>10.752025361042621</v>
+        <v>1E-4</v>
       </c>
       <c r="O4">
-        <v>1E-4</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
         <v>0</v>
       </c>
-      <c r="S4" t="s">
-        <v>52</v>
+      <c r="R4" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4">
+        <v>30</v>
       </c>
       <c r="T4">
-        <v>30</v>
+        <f>10.6/12*1.07/2</f>
+        <v>0.47258333333333336</v>
       </c>
       <c r="U4">
-        <f>10.6/24.6*1.07/2</f>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V4">
         <f>4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
-      <c r="W4">
+      <c r="V4">
         <f>0.00000058</f>
         <v>5.7999999999999995E-7</v>
       </c>
-      <c r="X4">
+      <c r="W4">
         <v>0.43</v>
       </c>
-      <c r="Y4" s="4">
-        <f>X4*1.066</f>
+      <c r="X4" s="4">
+        <f>W4*1.066</f>
         <v>0.45838000000000001</v>
       </c>
+      <c r="Y4">
+        <f>X4 *24</f>
+        <v>11.00112</v>
+      </c>
       <c r="Z4">
-        <f>Y4 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="AA4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AB4">
+        <v>1E-4</v>
+      </c>
+      <c r="AC4">
         <v>1</v>
       </c>
-      <c r="AC4">
-        <v>1E-4</v>
-      </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
         <f>10*0.103714686</f>
         <v>1.03714686</v>
       </c>
+      <c r="AF4">
+        <v>1E-3</v>
+      </c>
       <c r="AG4">
-        <v>1E-3</v>
+        <f>0.000001</f>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AH4">
-        <f t="shared" ref="AH4:AH13" si="2">0.0000001</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI4">
         <v>1</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK4">
+      <c r="AI4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ4">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:36">
       <c r="B5">
         <v>2</v>
       </c>
@@ -3758,103 +3746,103 @@
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I5">
+        <f>H5/F5*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J5">
-        <f t="shared" ref="J5:J9" si="3">H5/F5*1000</f>
-        <v>0.14336033814723495</v>
+        <f t="shared" ref="J5:J9" si="2">I5*7.5</f>
+        <v>1.0752025361042621</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K9" si="4">J5*7.5</f>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L5">
-        <f>K5/1000</f>
+        <f>J5/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
-      <c r="M5" s="4">
+      <c r="L5" s="4">
         <v>10</v>
       </c>
+      <c r="M5">
+        <f>L5*J5</f>
+        <v>10.752025361042621</v>
+      </c>
       <c r="N5">
-        <f>M5*K5</f>
-        <v>10.752025361042621</v>
+        <v>1E-4</v>
       </c>
       <c r="O5">
-        <v>1E-4</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" t="s">
-        <v>52</v>
+      <c r="R5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5">
+        <v>30</v>
       </c>
       <c r="T5">
-        <v>30</v>
+        <f t="shared" ref="T5:T9" si="3">10.6/12*1.07/2</f>
+        <v>0.47258333333333336</v>
       </c>
       <c r="U5">
-        <f t="shared" ref="U5:U13" si="5">10.6/24.6*1.07/2</f>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V5">
         <f>4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V13" si="4">0.00000058</f>
+        <v>5.7999999999999995E-7</v>
+      </c>
       <c r="W5">
-        <f t="shared" ref="W5:W13" si="6">0.00000058</f>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X5">
         <v>0.43</v>
       </c>
-      <c r="Y5" s="4">
-        <f>X5*1.066</f>
+      <c r="X5" s="4">
+        <f>W5*1.066</f>
         <v>0.45838000000000001</v>
       </c>
+      <c r="Y5">
+        <f>X5 *24</f>
+        <v>11.00112</v>
+      </c>
       <c r="Z5">
-        <f>Y5 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="AA5">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>1E-4</v>
       </c>
       <c r="AC5">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <f t="shared" ref="AE5:AE13" si="5">10*0.103714686</f>
+        <v>1.03714686</v>
       </c>
       <c r="AF5">
-        <f t="shared" ref="AF5:AF13" si="7">10*0.103714686</f>
-        <v>1.03714686</v>
+        <v>1E-3</v>
       </c>
       <c r="AG5">
-        <v>1E-3</v>
+        <f t="shared" ref="AG5:AG13" si="6">0.000001</f>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI5">
         <v>1</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK5">
+      <c r="AI5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ5">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:36">
       <c r="B6">
         <v>3</v>
       </c>
@@ -3875,103 +3863,103 @@
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I6">
+        <f>H6/F6*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J6">
+        <f t="shared" si="2"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:K9" si="7">J6/1000</f>
+        <v>1.075202536104262E-3</v>
+      </c>
+      <c r="L6" s="4">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <f t="shared" ref="M6" si="8">L6*J6</f>
+        <v>10.752025361042621</v>
+      </c>
+      <c r="N6">
+        <v>1E-4</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6">
+        <v>30</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>0.14336033814723495</v>
-      </c>
-      <c r="K6">
+        <v>0.47258333333333336</v>
+      </c>
+      <c r="U6">
+        <f t="shared" ref="U6:U9" si="9">4.3 /1000000 *1.07</f>
+        <v>4.6009999999999997E-6</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="4"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L6">
-        <f t="shared" ref="L6:L9" si="8">K6/1000</f>
-        <v>1.075202536104262E-3</v>
-      </c>
-      <c r="M6" s="4">
-        <v>10</v>
-      </c>
-      <c r="N6">
-        <f t="shared" ref="N6" si="9">M6*K6</f>
-        <v>10.752025361042621</v>
-      </c>
-      <c r="O6">
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W6">
+        <v>0.43</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" ref="X6:X8" si="10">W6*1.066</f>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" ref="Y6:Y8" si="11">X6 *24</f>
+        <v>11.00112</v>
+      </c>
+      <c r="Z6">
+        <v>0.06</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
         <v>1E-4</v>
       </c>
-      <c r="P6">
-        <v>10</v>
-      </c>
-      <c r="Q6">
+      <c r="AC6">
         <v>1</v>
       </c>
-      <c r="R6">
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="S6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6">
-        <v>30</v>
-      </c>
-      <c r="U6">
+      <c r="AE6">
         <f t="shared" si="5"/>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V6">
-        <f t="shared" ref="V6:V9" si="10">4.3 /1000000 *1.07</f>
-        <v>4.6009999999999997E-6</v>
-      </c>
-      <c r="W6">
+        <v>1.03714686</v>
+      </c>
+      <c r="AF6">
+        <v>1E-3</v>
+      </c>
+      <c r="AG6">
         <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X6">
-        <v>0.43</v>
-      </c>
-      <c r="Y6" s="4">
-        <f t="shared" ref="Y6:Y8" si="11">X6*1.066</f>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z6">
-        <f t="shared" ref="Z6:Z8" si="12">Y6 *24</f>
-        <v>11.00112</v>
-      </c>
-      <c r="AA6">
-        <v>0.06</v>
-      </c>
-      <c r="AB6">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AH6">
         <v>1</v>
       </c>
-      <c r="AC6">
-        <v>1E-4</v>
-      </c>
-      <c r="AD6">
-        <v>1</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
-      </c>
-      <c r="AG6">
-        <v>1E-3</v>
-      </c>
-      <c r="AH6">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK6">
+      <c r="AI6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ6">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:36">
       <c r="B7">
         <v>4</v>
       </c>
@@ -3992,103 +3980,103 @@
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I7">
+        <f>H7/F7*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J7">
+        <f t="shared" si="2"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="7"/>
+        <v>1.075202536104262E-3</v>
+      </c>
+      <c r="L7" s="4">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <f>L7*J7</f>
+        <v>10.752025361042621</v>
+      </c>
+      <c r="N7">
+        <v>1E-4</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>50</v>
+      </c>
+      <c r="S7">
+        <v>30</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="3"/>
-        <v>0.14336033814723495</v>
-      </c>
-      <c r="K7">
+        <v>0.47258333333333336</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="9"/>
+        <v>4.6009999999999997E-6</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="4"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="8"/>
-        <v>1.075202536104262E-3</v>
-      </c>
-      <c r="M7" s="4">
-        <v>10</v>
-      </c>
-      <c r="N7">
-        <f>M7*K7</f>
-        <v>10.752025361042621</v>
-      </c>
-      <c r="O7">
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W7">
+        <v>0.43</v>
+      </c>
+      <c r="X7" s="4">
+        <f t="shared" si="10"/>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="11"/>
+        <v>11.00112</v>
+      </c>
+      <c r="Z7">
+        <v>0.06</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
         <v>1E-4</v>
       </c>
-      <c r="P7">
-        <v>10</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
+      <c r="AC7">
         <v>0</v>
-      </c>
-      <c r="S7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T7">
-        <v>30</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="5"/>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="10"/>
-        <v>4.6009999999999997E-6</v>
-      </c>
-      <c r="W7">
-        <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X7">
-        <v>0.43</v>
-      </c>
-      <c r="Y7" s="4">
-        <f t="shared" si="11"/>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z7">
-        <f t="shared" si="12"/>
-        <v>11.00112</v>
-      </c>
-      <c r="AA7">
-        <v>0.06</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>1E-4</v>
       </c>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.03714686</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
+        <v>1E-3</v>
       </c>
       <c r="AG7">
-        <v>1E-3</v>
+        <f t="shared" si="6"/>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI7">
         <v>1</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK7">
+      <c r="AI7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ7">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:36">
       <c r="B8">
         <v>5</v>
       </c>
@@ -4109,103 +4097,103 @@
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I8">
+        <f>H8/F8*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J8">
+        <f t="shared" si="2"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="7"/>
+        <v>1.075202536104262E-3</v>
+      </c>
+      <c r="L8" s="4">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <f t="shared" ref="M8" si="12">L8*J8</f>
+        <v>10.752025361042621</v>
+      </c>
+      <c r="N8">
+        <v>1E-4</v>
+      </c>
+      <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8">
+        <v>30</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="3"/>
-        <v>0.14336033814723495</v>
-      </c>
-      <c r="K8">
+        <v>0.47258333333333336</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="9"/>
+        <v>4.6009999999999997E-6</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="4"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="8"/>
-        <v>1.075202536104262E-3</v>
-      </c>
-      <c r="M8" s="4">
-        <v>10</v>
-      </c>
-      <c r="N8">
-        <f t="shared" ref="N8" si="13">M8*K8</f>
-        <v>10.752025361042621</v>
-      </c>
-      <c r="O8">
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W8">
+        <v>0.43</v>
+      </c>
+      <c r="X8" s="4">
+        <f t="shared" si="10"/>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="11"/>
+        <v>11.00112</v>
+      </c>
+      <c r="Z8">
+        <v>0.06</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
         <v>1E-4</v>
       </c>
-      <c r="P8">
-        <v>10</v>
-      </c>
-      <c r="Q8">
+      <c r="AC8">
         <v>1</v>
       </c>
-      <c r="R8">
+      <c r="AD8">
         <v>0</v>
       </c>
-      <c r="S8" t="s">
-        <v>52</v>
-      </c>
-      <c r="T8">
-        <v>30</v>
-      </c>
-      <c r="U8">
+      <c r="AE8">
         <f t="shared" si="5"/>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="10"/>
-        <v>4.6009999999999997E-6</v>
-      </c>
-      <c r="W8">
+        <v>1.03714686</v>
+      </c>
+      <c r="AF8">
+        <v>1E-3</v>
+      </c>
+      <c r="AG8">
         <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X8">
-        <v>0.43</v>
-      </c>
-      <c r="Y8" s="4">
-        <f t="shared" si="11"/>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z8">
-        <f t="shared" si="12"/>
-        <v>11.00112</v>
-      </c>
-      <c r="AA8">
-        <v>0.06</v>
-      </c>
-      <c r="AB8">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AH8">
         <v>1</v>
       </c>
-      <c r="AC8">
-        <v>1E-4</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
-      </c>
-      <c r="AG8">
-        <v>1E-3</v>
-      </c>
-      <c r="AH8">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI8">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK8">
+      <c r="AI8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ8">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:36">
       <c r="B9">
         <v>6</v>
       </c>
@@ -4220,109 +4208,109 @@
         <v>1419.5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I9">
+        <f>H9/F9*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J9">
+        <f t="shared" si="2"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>1.075202536104262E-3</v>
+      </c>
+      <c r="L9" s="4">
+        <v>10</v>
+      </c>
+      <c r="M9">
+        <f>L9*J9</f>
+        <v>10.752025361042621</v>
+      </c>
+      <c r="N9">
+        <v>1E-4</v>
+      </c>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9">
+        <v>30</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="3"/>
-        <v>0.14336033814723495</v>
-      </c>
-      <c r="K9">
+        <v>0.47258333333333336</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="9"/>
+        <v>4.6009999999999997E-6</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="4"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="8"/>
-        <v>1.075202536104262E-3</v>
-      </c>
-      <c r="M9" s="4">
-        <v>10</v>
-      </c>
-      <c r="N9">
-        <f>M9*K9</f>
-        <v>10.752025361042621</v>
-      </c>
-      <c r="O9">
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W9">
+        <v>0.43</v>
+      </c>
+      <c r="X9" s="4">
+        <f>W9*1.066</f>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y9">
+        <f>X9 *24</f>
+        <v>11.00112</v>
+      </c>
+      <c r="Z9">
+        <v>0.06</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
         <v>1E-4</v>
       </c>
-      <c r="P9">
-        <v>10</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
+      <c r="AC9">
         <v>0</v>
-      </c>
-      <c r="S9" t="s">
-        <v>52</v>
-      </c>
-      <c r="T9">
-        <v>30</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="5"/>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="10"/>
-        <v>4.6009999999999997E-6</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X9">
-        <v>0.43</v>
-      </c>
-      <c r="Y9" s="4">
-        <f>X9*1.066</f>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z9">
-        <f>Y9 *24</f>
-        <v>11.00112</v>
-      </c>
-      <c r="AA9">
-        <v>0.06</v>
-      </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>1E-4</v>
       </c>
       <c r="AD9">
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.03714686</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
+        <v>1E-3</v>
       </c>
       <c r="AG9">
-        <v>1E-3</v>
+        <f t="shared" si="6"/>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI9">
         <v>1</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK9">
+      <c r="AI9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ9">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:36">
       <c r="B10">
         <v>7</v>
       </c>
@@ -4337,108 +4325,108 @@
         <v>1419.5</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I10">
+        <f>H10/F10*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J10">
-        <f t="shared" ref="J10:J11" si="14">H10/F10*1000</f>
-        <v>0.14336033814723495</v>
+        <f t="shared" ref="J10:J11" si="13">I10*7.5</f>
+        <v>1.0752025361042621</v>
       </c>
       <c r="K10">
-        <f t="shared" ref="K10:K11" si="15">J10*7.5</f>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L10">
-        <f t="shared" ref="L10:L11" si="16">K10/1000</f>
+        <f t="shared" ref="K10:K11" si="14">J10/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
-      <c r="M10" s="4">
+      <c r="L10" s="4">
         <v>10</v>
       </c>
+      <c r="M10">
+        <f>L10*J10</f>
+        <v>10.752025361042621</v>
+      </c>
       <c r="N10">
-        <f>M10*K10</f>
-        <v>10.752025361042621</v>
+        <v>1E-4</v>
       </c>
       <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10">
+        <v>30</v>
+      </c>
+      <c r="T10" s="21">
+        <v>1E-3</v>
+      </c>
+      <c r="U10">
+        <f t="shared" ref="U10:U11" si="15">4.3 /1000000 *1.07</f>
+        <v>4.6009999999999997E-6</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="4"/>
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W10">
+        <v>0.43</v>
+      </c>
+      <c r="X10" s="4">
+        <f>W10*1.066</f>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y10">
+        <f>X10 *24</f>
+        <v>11.00112</v>
+      </c>
+      <c r="Z10">
+        <v>0.06</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
         <v>1E-4</v>
       </c>
-      <c r="P10">
-        <v>10</v>
-      </c>
-      <c r="Q10">
+      <c r="AC10">
         <v>1</v>
       </c>
-      <c r="R10">
+      <c r="AD10">
         <v>0</v>
       </c>
-      <c r="S10" t="s">
-        <v>52</v>
-      </c>
-      <c r="T10">
-        <v>30</v>
-      </c>
-      <c r="U10" s="21">
+      <c r="AE10">
+        <f t="shared" si="5"/>
+        <v>1.03714686</v>
+      </c>
+      <c r="AF10">
         <v>1E-3</v>
       </c>
-      <c r="V10">
-        <f t="shared" ref="V10:V11" si="17">4.3 /1000000 *1.07</f>
-        <v>4.6009999999999997E-6</v>
-      </c>
-      <c r="W10">
+      <c r="AG10">
         <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X10">
-        <v>0.43</v>
-      </c>
-      <c r="Y10" s="4">
-        <f>X10*1.066</f>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z10">
-        <f>Y10 *24</f>
-        <v>11.00112</v>
-      </c>
-      <c r="AA10">
-        <v>0.06</v>
-      </c>
-      <c r="AB10">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AH10">
         <v>1</v>
       </c>
-      <c r="AC10">
-        <v>1E-4</v>
-      </c>
-      <c r="AD10">
-        <v>1</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
-      </c>
-      <c r="AG10">
-        <v>1E-3</v>
-      </c>
-      <c r="AH10">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI10">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK10">
+      <c r="AI10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ10">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:36">
       <c r="B11">
         <v>8</v>
       </c>
@@ -4453,108 +4441,108 @@
         <v>1419.5</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I11">
+        <f>H11/F11*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J11">
+        <f t="shared" si="13"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="14"/>
-        <v>0.14336033814723495</v>
-      </c>
-      <c r="K11">
+        <v>1.075202536104262E-3</v>
+      </c>
+      <c r="L11" s="4">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <f>L11*J11</f>
+        <v>10.752025361042621</v>
+      </c>
+      <c r="N11">
+        <v>1E-4</v>
+      </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>50</v>
+      </c>
+      <c r="S11">
+        <v>30</v>
+      </c>
+      <c r="T11" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="U11">
         <f t="shared" si="15"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="16"/>
-        <v>1.075202536104262E-3</v>
-      </c>
-      <c r="M11" s="4">
-        <v>10</v>
-      </c>
-      <c r="N11">
-        <f>M11*K11</f>
-        <v>10.752025361042621</v>
-      </c>
-      <c r="O11">
+        <v>4.6009999999999997E-6</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="4"/>
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W11">
+        <v>0.43</v>
+      </c>
+      <c r="X11" s="4">
+        <f>W11*1.066</f>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y11">
+        <f>X11 *24</f>
+        <v>11.00112</v>
+      </c>
+      <c r="Z11">
+        <v>0.06</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
         <v>1E-4</v>
       </c>
-      <c r="P11">
-        <v>10</v>
-      </c>
-      <c r="Q11">
+      <c r="AC11">
         <v>1</v>
       </c>
-      <c r="R11">
+      <c r="AD11">
         <v>0</v>
       </c>
-      <c r="S11" t="s">
-        <v>52</v>
-      </c>
-      <c r="T11">
-        <v>30</v>
-      </c>
-      <c r="U11" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="17"/>
-        <v>4.6009999999999997E-6</v>
-      </c>
-      <c r="W11">
+      <c r="AE11">
+        <f t="shared" si="5"/>
+        <v>1.03714686</v>
+      </c>
+      <c r="AF11">
+        <v>1E-3</v>
+      </c>
+      <c r="AG11">
         <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X11">
-        <v>0.43</v>
-      </c>
-      <c r="Y11" s="4">
-        <f>X11*1.066</f>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z11">
-        <f>Y11 *24</f>
-        <v>11.00112</v>
-      </c>
-      <c r="AA11">
-        <v>0.06</v>
-      </c>
-      <c r="AB11">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AH11">
         <v>1</v>
       </c>
-      <c r="AC11">
-        <v>1E-4</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
-      </c>
-      <c r="AG11">
-        <v>1E-3</v>
-      </c>
-      <c r="AH11">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI11">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK11">
+      <c r="AI11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ11">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:36">
       <c r="B12">
         <v>9</v>
       </c>
@@ -4569,108 +4557,108 @@
         <v>1419.5</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I12">
+        <f>H12/F12*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J12">
-        <f t="shared" ref="J12:J13" si="18">H12/F12*1000</f>
-        <v>0.14336033814723495</v>
+        <f t="shared" ref="J12:J13" si="16">I12*7.5</f>
+        <v>1.0752025361042621</v>
       </c>
       <c r="K12">
-        <f t="shared" ref="K12:K13" si="19">J12*7.5</f>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L12">
-        <f t="shared" ref="L12:L13" si="20">K12/1000</f>
+        <f t="shared" ref="K12:K13" si="17">J12/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
-      <c r="M12" s="4">
+      <c r="L12" s="4">
         <v>10</v>
       </c>
+      <c r="M12">
+        <f>L12*J12</f>
+        <v>10.752025361042621</v>
+      </c>
       <c r="N12">
-        <f>M12*K12</f>
-        <v>10.752025361042621</v>
+        <v>1E-4</v>
       </c>
       <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>50</v>
+      </c>
+      <c r="S12">
+        <v>30</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T12:T13" si="18">10.6/12*1.07/2</f>
+        <v>0.47258333333333336</v>
+      </c>
+      <c r="U12" s="21">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="4"/>
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W12">
+        <v>0.43</v>
+      </c>
+      <c r="X12" s="4">
+        <f>W12*1.066</f>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y12">
+        <f>X12 *24</f>
+        <v>11.00112</v>
+      </c>
+      <c r="Z12">
+        <v>0.06</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
         <v>1E-4</v>
       </c>
-      <c r="P12">
-        <v>10</v>
-      </c>
-      <c r="Q12">
+      <c r="AC12">
         <v>1</v>
       </c>
-      <c r="R12">
+      <c r="AD12">
         <v>0</v>
       </c>
-      <c r="S12" t="s">
-        <v>52</v>
-      </c>
-      <c r="T12">
-        <v>30</v>
-      </c>
-      <c r="U12" s="22">
+      <c r="AE12">
         <f t="shared" si="5"/>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V12" s="21">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="W12">
+        <v>1.03714686</v>
+      </c>
+      <c r="AF12">
+        <v>1E-3</v>
+      </c>
+      <c r="AG12">
         <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X12">
-        <v>0.43</v>
-      </c>
-      <c r="Y12" s="4">
-        <f>X12*1.066</f>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z12">
-        <f>Y12 *24</f>
-        <v>11.00112</v>
-      </c>
-      <c r="AA12">
-        <v>0.06</v>
-      </c>
-      <c r="AB12">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AH12">
         <v>1</v>
       </c>
-      <c r="AC12">
-        <v>1E-4</v>
-      </c>
-      <c r="AD12">
-        <v>1</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
-      </c>
-      <c r="AG12">
-        <v>1E-3</v>
-      </c>
-      <c r="AH12">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI12">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK12">
+      <c r="AI12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ12">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:36">
       <c r="B13">
         <v>10</v>
       </c>
@@ -4685,109 +4673,109 @@
         <v>1419.5</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
+      <c r="I13">
+        <f>H13/F13*1000</f>
+        <v>0.14336033814723495</v>
+      </c>
       <c r="J13">
+        <f t="shared" si="16"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="17"/>
+        <v>1.075202536104262E-3</v>
+      </c>
+      <c r="L13" s="4">
+        <v>10</v>
+      </c>
+      <c r="M13">
+        <f>L13*J13</f>
+        <v>10.752025361042621</v>
+      </c>
+      <c r="N13">
+        <v>1E-4</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>50</v>
+      </c>
+      <c r="S13">
+        <v>30</v>
+      </c>
+      <c r="T13">
         <f t="shared" si="18"/>
-        <v>0.14336033814723495</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="19"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="20"/>
-        <v>1.075202536104262E-3</v>
-      </c>
-      <c r="M13" s="4">
-        <v>10</v>
-      </c>
-      <c r="N13">
-        <f>M13*K13</f>
-        <v>10.752025361042621</v>
-      </c>
-      <c r="O13">
+        <v>0.47258333333333336</v>
+      </c>
+      <c r="U13" s="21">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="4"/>
+        <v>5.7999999999999995E-7</v>
+      </c>
+      <c r="W13">
+        <v>0.43</v>
+      </c>
+      <c r="X13" s="4">
+        <f>W13*1.066</f>
+        <v>0.45838000000000001</v>
+      </c>
+      <c r="Y13">
+        <f>X13 *24</f>
+        <v>11.00112</v>
+      </c>
+      <c r="Z13">
+        <v>0.06</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
         <v>1E-4</v>
       </c>
-      <c r="P13">
-        <v>10</v>
-      </c>
-      <c r="Q13">
+      <c r="AC13">
         <v>1</v>
       </c>
-      <c r="R13">
+      <c r="AD13">
         <v>0</v>
       </c>
-      <c r="S13" t="s">
-        <v>52</v>
-      </c>
-      <c r="T13">
-        <v>30</v>
-      </c>
-      <c r="U13" s="22">
+      <c r="AE13">
         <f t="shared" si="5"/>
-        <v>0.23052845528455285</v>
-      </c>
-      <c r="V13" s="21">
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="W13">
+        <v>1.03714686</v>
+      </c>
+      <c r="AF13">
+        <v>1E-3</v>
+      </c>
+      <c r="AG13">
         <f t="shared" si="6"/>
-        <v>5.7999999999999995E-7</v>
-      </c>
-      <c r="X13">
-        <v>0.43</v>
-      </c>
-      <c r="Y13" s="4">
-        <f>X13*1.066</f>
-        <v>0.45838000000000001</v>
-      </c>
-      <c r="Z13">
-        <f>Y13 *24</f>
-        <v>11.00112</v>
-      </c>
-      <c r="AA13">
-        <v>0.06</v>
-      </c>
-      <c r="AB13">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AH13">
         <v>1</v>
       </c>
-      <c r="AC13">
-        <v>1E-4</v>
-      </c>
-      <c r="AD13">
-        <v>1</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="7"/>
-        <v>1.03714686</v>
-      </c>
-      <c r="AG13">
-        <v>1E-3</v>
-      </c>
-      <c r="AH13">
-        <f t="shared" si="2"/>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="AI13">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK13">
+      <c r="AI13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ13">
         <v>9.375E-2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AK3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}"/>
+  <autoFilter ref="A3:AJ3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4805,7 +4793,7 @@
   <sheetData>
     <row r="1" spans="2:21">
       <c r="B1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:21">
@@ -4888,38 +4876,38 @@
     </row>
     <row r="16" spans="2:21">
       <c r="L16" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="12:20">
       <c r="L17" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
         <v>35</v>
       </c>
-      <c r="O17" t="s">
-        <v>39</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>36</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>37</v>
       </c>
-      <c r="R17" t="s">
-        <v>38</v>
-      </c>
       <c r="T17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="12:20">
       <c r="L18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -4940,12 +4928,12 @@
     </row>
     <row r="19" spans="12:20">
       <c r="L19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="12:20">
       <c r="L20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="12:20">
@@ -4954,43 +4942,43 @@
         <v>227</v>
       </c>
       <c r="M21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="12:20">
       <c r="L22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="12:20">
       <c r="L25" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N25" t="s">
+        <v>34</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
         <v>35</v>
       </c>
-      <c r="O25" t="s">
-        <v>39</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>36</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>37</v>
       </c>
-      <c r="R25" t="s">
-        <v>38</v>
-      </c>
       <c r="T25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="12:20">
       <c r="L26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O26">
         <v>2</v>
@@ -5014,53 +5002,53 @@
         <v>60</v>
       </c>
       <c r="M27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="12:20">
       <c r="L28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="12:20">
       <c r="L31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="12:20" ht="18">
       <c r="L32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="10:20">
       <c r="L33" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N33" t="s">
+        <v>34</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
         <v>35</v>
       </c>
-      <c r="O33" t="s">
-        <v>39</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>37</v>
       </c>
-      <c r="R33" t="s">
-        <v>38</v>
-      </c>
       <c r="T33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="10:20">
       <c r="L34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -5083,7 +5071,7 @@
       <c r="J35" s="11"/>
       <c r="K35" s="10"/>
       <c r="L35" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="10:20">
@@ -5101,7 +5089,7 @@
     </row>
     <row r="40" spans="10:20">
       <c r="M40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="10:20">
@@ -5109,25 +5097,25 @@
         <v>2.6</v>
       </c>
       <c r="N41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P41">
         <v>2.6</v>
       </c>
       <c r="Q41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="10:20">
       <c r="L42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M42">
         <f>12+1.8+0.5*16+0.2*14</f>
         <v>24.6</v>
       </c>
       <c r="N42" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="10:20">
@@ -5138,7 +5126,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="3:14">
@@ -5147,10 +5135,10 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="M51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="3:14">
@@ -5159,7 +5147,7 @@
         <v>2.032520325203252E-10</v>
       </c>
       <c r="M54" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="3:14">
@@ -5176,81 +5164,81 @@
     </row>
     <row r="58" spans="3:14">
       <c r="L58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="3:14" ht="18">
       <c r="L59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="3:14">
       <c r="C60" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D60" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M60">
         <f>5*12+7+2*16+14</f>
         <v>113</v>
       </c>
       <c r="N60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="3:14">
       <c r="D61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E61" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="3:14">
       <c r="C62" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D62">
         <v>7.5</v>
       </c>
       <c r="E62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L62" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="3:14">
       <c r="C63" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D63">
         <v>5.9</v>
       </c>
       <c r="E63" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L63" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="3:14">
       <c r="C64" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D64" s="13">
         <f>D62-D63</f>
         <v>1.5999999999999996</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F64" s="13"/>
       <c r="K64">
@@ -5258,117 +5246,117 @@
         <v>4.25</v>
       </c>
       <c r="L64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="3:13">
       <c r="C65" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D65" s="13">
         <f>D62+D63</f>
         <v>13.4</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F65" s="13"/>
       <c r="L65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="3:13">
       <c r="C66" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D66">
         <f>D62/227.172/1000</f>
         <v>3.3014632084940045E-5</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L66">
         <f>4.25*32</f>
         <v>136</v>
       </c>
       <c r="M66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="3:13">
       <c r="C67" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D67">
         <f>D63/227.172/1000</f>
         <v>2.5971510573486172E-5</v>
       </c>
       <c r="E67" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L67">
         <f>L66/M60</f>
         <v>1.2035398230088497</v>
       </c>
       <c r="M67" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="3:13">
       <c r="C68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D68">
         <f>D66*24.6</f>
         <v>8.1215994928952515E-4</v>
       </c>
       <c r="E68" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L68" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="3:13">
       <c r="C69" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D69">
         <f>D67*24.6</f>
         <v>6.388991601077599E-4</v>
       </c>
       <c r="E69" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="3:13">
       <c r="C70" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D70">
         <f>D68*1.075/1.05</f>
         <v>8.3149709093927569E-4</v>
       </c>
       <c r="E70" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="3:13">
       <c r="C71" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D71">
         <f>D69*1.075/1.05</f>
         <v>6.5411104487223025E-4</v>
       </c>
       <c r="E71" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="3:13">
       <c r="C75" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="3:13">
@@ -5376,7 +5364,7 @@
         <v>0.33</v>
       </c>
       <c r="E76" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="3:13">
@@ -5384,7 +5372,7 @@
         <v>0.73</v>
       </c>
       <c r="E77" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="3:13">
@@ -5393,7 +5381,7 @@
         <v>3.3000000000000002E-7</v>
       </c>
       <c r="E78" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="3:13">
@@ -5402,7 +5390,7 @@
         <v>7.3E-7</v>
       </c>
       <c r="E79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="3:13">
@@ -5411,7 +5399,7 @@
         <v>2.7500000000000001E-8</v>
       </c>
       <c r="E80" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="4:12">
@@ -5420,7 +5408,7 @@
         <v>6.0833333333333329E-8</v>
       </c>
       <c r="E81" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="4:12">
@@ -5429,7 +5417,7 @@
         <v>5.5000000000000014E-3</v>
       </c>
       <c r="E82" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="4:12">
@@ -5438,7 +5426,7 @@
         <v>1.2166666666666666E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84" spans="4:12">
@@ -5447,7 +5435,7 @@
         <v>0.13530000000000003</v>
       </c>
       <c r="E84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="4:12">
@@ -5456,7 +5444,7 @@
         <v>0.29930000000000001</v>
       </c>
       <c r="E85" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="4:12">
@@ -5465,7 +5453,7 @@
         <v>0.12885714285714289</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" spans="4:12">
@@ -5474,7 +5462,7 @@
         <v>0.28504761904761905</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89" spans="4:12">
@@ -5483,10 +5471,10 @@
         <v>8.4242681454371637E-2</v>
       </c>
       <c r="E89" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="4:12">
@@ -5494,13 +5482,13 @@
         <v>6.905E-6</v>
       </c>
       <c r="E90" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K90">
         <v>0.35</v>
       </c>
       <c r="L90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="4:12">
@@ -5509,14 +5497,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E91" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K91">
         <f>K90/1000000/24.6</f>
         <v>1.4227642276422762E-8</v>
       </c>
       <c r="L91" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="4:12">
@@ -5525,14 +5513,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E92" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K92">
         <f>K91*1.05</f>
         <v>1.4939024390243901E-8</v>
       </c>
       <c r="L92" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="4:12">
@@ -5541,7 +5529,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L93" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="4:12">
@@ -5550,12 +5538,12 @@
         <v>1.4939024390243901E-3</v>
       </c>
       <c r="L94" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="4:12">
       <c r="E96" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="4:14">
@@ -5563,7 +5551,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="98" spans="4:14">
@@ -5571,13 +5559,13 @@
         <v>9.09</v>
       </c>
       <c r="E98" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F98" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L98" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="4:14">
@@ -5585,20 +5573,20 @@
         <v>7.58</v>
       </c>
       <c r="E99" t="s">
+        <v>124</v>
+      </c>
+      <c r="F99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>128</v>
       </c>
       <c r="L99">
         <f>AVERAGE(D127, D86:D87,D70)</f>
         <v>0.10371468607138892</v>
       </c>
       <c r="M99" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N99" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="100" spans="4:14">
@@ -5606,13 +5594,13 @@
         <v>7.96</v>
       </c>
       <c r="E100" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F100" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N100" s="15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="101" spans="4:14">
@@ -5620,10 +5608,10 @@
         <v>6.52</v>
       </c>
       <c r="E101" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F101" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="102" spans="4:14">
@@ -5631,10 +5619,10 @@
         <v>4.71</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F102" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H102">
         <f>AVERAGE(D102:D105)</f>
@@ -5646,10 +5634,10 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F103" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104" spans="4:14">
@@ -5657,10 +5645,10 @@
         <v>4.18</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F104" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="4:14">
@@ -5668,10 +5656,10 @@
         <v>4.13</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F105" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="4:14">
@@ -5679,7 +5667,7 @@
         <v>4.3</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107" spans="4:14">
@@ -5687,7 +5675,7 @@
         <v>0.5</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="108" spans="4:14">
@@ -5695,7 +5683,7 @@
         <v>14.9</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="4:14">
@@ -5703,7 +5691,7 @@
         <v>1.9</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110" spans="4:14">
@@ -5711,7 +5699,7 @@
         <v>12.4</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="111" spans="4:14">
@@ -5719,7 +5707,7 @@
         <v>1.2</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112" spans="4:14">
@@ -5727,7 +5715,7 @@
         <v>0.01</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="113" spans="4:5">
@@ -5735,7 +5723,7 @@
         <v>8.1</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114" spans="4:5">
@@ -5743,12 +5731,12 @@
         <v>0.15336312500000002</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="115" spans="4:5">
       <c r="E115" s="17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116" spans="4:5">
@@ -5757,7 +5745,7 @@
         <v>8.3333333333333344E-7</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" spans="4:5">
@@ -5766,7 +5754,7 @@
         <v>6.7499999999999993E-4</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="4:5">
@@ -5775,7 +5763,7 @@
         <v>1.2780260416666668E-5</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="119" spans="4:5">
@@ -5784,7 +5772,7 @@
         <v>1.9190174630589144E-7</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="4:5">
@@ -5793,7 +5781,7 @@
         <v>1.5544041450777204E-4</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="4:5">
@@ -5802,7 +5790,7 @@
         <v>2.9430651506428716E-6</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="4:5">
@@ -5811,7 +5799,7 @@
         <v>7.8008839961744482E-6</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="123" spans="4:5">
@@ -5820,7 +5808,7 @@
         <v>6.3187160369013026E-3</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="4:5">
@@ -5829,7 +5817,7 @@
         <v>1.1963679474158013E-4</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="4:5">
@@ -5838,7 +5826,7 @@
         <v>7.9866193294166962E-6</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="4:5">
@@ -5847,7 +5835,7 @@
         <v>6.4691616568275231E-3</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="4:5">
@@ -5856,12 +5844,12 @@
         <v>1.224852898544749E-4</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="4:6" ht="198">
       <c r="D130" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131" spans="4:6">
@@ -5870,10 +5858,10 @@
         <v>1.6000000000000003E-5</v>
       </c>
       <c r="E131" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F131" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="132" spans="4:6">
@@ -5882,10 +5870,10 @@
         <v>4.5714285714285719E-6</v>
       </c>
       <c r="E132" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F132" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133" spans="4:6">
@@ -5893,10 +5881,10 @@
         <v>630000</v>
       </c>
       <c r="E133" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F133" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="4:6">
@@ -5905,10 +5893,10 @@
         <v>6.3E+17</v>
       </c>
       <c r="E134" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F134" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="135" spans="4:6">
@@ -5917,10 +5905,10 @@
         <v>2880000000000.0005</v>
       </c>
       <c r="E135" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F135" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="136" spans="4:6">
@@ -5929,10 +5917,10 @@
         <v>227</v>
       </c>
       <c r="E136" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F136" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="137" spans="4:6">
@@ -5941,10 +5929,10 @@
         <v>653760000000000.13</v>
       </c>
       <c r="E137" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F137" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="138" spans="4:6">
@@ -5953,10 +5941,10 @@
         <v>653760000000.00012</v>
       </c>
       <c r="E138" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F138" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="139" spans="4:6">
@@ -5965,10 +5953,10 @@
         <v>653760000.00000012</v>
       </c>
       <c r="E139" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F139" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723E973C-CDD4-4127-A868-8EB1E54025E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9997450B-502C-46B8-9820-CCAA9DD35877}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
@@ -39,23 +39,18 @@
     <author>tc={4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}</author>
     <author>tc={8B1BECD1-664B-894E-902F-58308D659DA9}</author>
     <author>tc={944B0A6E-7F35-8040-8354-541096ED2DBE}</author>
-    <author>tc={009AF6C5-B9AC-7541-9E56-015D22C54F6F}</author>
     <author>tc={0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}</author>
     <author>tc={3C0608B8-171F-064A-822A-A3CC6DDC9FC4}</author>
     <author>tc={4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}</author>
-    <author>tc={B40E02FA-A395-684A-865E-E43D81BF9EF7}</author>
     <author>tc={8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}</author>
     <author>tc={D578DC42-15AA-9242-8F7A-DCCCBD7DB327}</author>
     <author>tc={D9858DC7-D04C-4A4F-872C-0C59D675639A}</author>
-    <author>tc={507182A8-A16E-3B46-A78B-C475F7E79FFC}</author>
     <author>tc={28910C3F-267C-EF48-8C2C-F6C895522D82}</author>
     <author>tc={E7A076DC-8E76-1148-951F-1F3AE0C081A3}</author>
     <author>tc={8ABD701E-78D0-4A47-8F33-59280C42BAAB}</author>
-    <author>tc={C8D487C4-854D-254E-A24C-BB3F3463062E}</author>
     <author>tc={E68EDC32-0C11-F24F-BC92-6599E44DEE2B}</author>
     <author>tc={03DDDF21-1FDE-1A44-92CB-02C9D1E67681}</author>
     <author>tc={74D124C3-18A4-4549-83DD-7E733D9BD57D}</author>
-    <author>tc={59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}</author>
   </authors>
   <commentList>
     <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{C7B782E2-F656-DB45-97AC-D2B1A4310A43}">
@@ -429,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE5" authorId="8" shapeId="0" xr:uid="{009AF6C5-B9AC-7541-9E56-015D22C54F6F}">
+    <comment ref="AE5" authorId="4" shapeId="0" xr:uid="{3A4E7E2B-C45D-41E9-96C1-3B0C321FF477}">
       <text>
         <r>
           <rPr>
@@ -446,7 +441,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="9" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
+    <comment ref="J6" authorId="8" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
       <text>
         <r>
           <rPr>
@@ -463,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="10" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
+    <comment ref="V6" authorId="9" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
       <text>
         <r>
           <rPr>
@@ -526,7 +521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z6" authorId="11" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
+    <comment ref="Z6" authorId="10" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
       <text>
         <r>
           <rPr>
@@ -543,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE6" authorId="12" shapeId="0" xr:uid="{B40E02FA-A395-684A-865E-E43D81BF9EF7}">
+    <comment ref="AE6" authorId="4" shapeId="0" xr:uid="{81C33CF6-277A-4464-8765-7CFDC40903D9}">
       <text>
         <r>
           <rPr>
@@ -560,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="13" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
+    <comment ref="J7" authorId="11" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
       <text>
         <r>
           <rPr>
@@ -577,7 +572,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V7" authorId="14" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
+    <comment ref="V7" authorId="12" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
       <text>
         <r>
           <rPr>
@@ -594,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z7" authorId="15" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
+    <comment ref="Z7" authorId="13" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
       <text>
         <r>
           <rPr>
@@ -611,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE7" authorId="16" shapeId="0" xr:uid="{507182A8-A16E-3B46-A78B-C475F7E79FFC}">
+    <comment ref="AE7" authorId="4" shapeId="0" xr:uid="{F5DBD1C4-1855-49B5-A8A2-512AEE391C65}">
       <text>
         <r>
           <rPr>
@@ -628,7 +623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="17" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
+    <comment ref="J8" authorId="14" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
       <text>
         <r>
           <rPr>
@@ -645,7 +640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V8" authorId="18" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
+    <comment ref="V8" authorId="15" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
       <text>
         <r>
           <rPr>
@@ -708,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z8" authorId="19" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
+    <comment ref="Z8" authorId="16" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
       <text>
         <r>
           <rPr>
@@ -725,70 +720,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE8" authorId="20" shapeId="0" xr:uid="{C8D487C4-854D-254E-A24C-BB3F3463062E}">
+    <comment ref="AE8" authorId="4" shapeId="0" xr:uid="{45A9C127-CEF7-4D99-93CE-A916236D9D99}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="21" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
+    <comment ref="J9" authorId="17" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
       <text>
         <r>
           <rPr>
@@ -805,7 +754,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V9" authorId="22" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
+    <comment ref="V9" authorId="18" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
       <text>
         <r>
           <rPr>
@@ -868,7 +817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z9" authorId="23" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
+    <comment ref="Z9" authorId="19" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
       <text>
         <r>
           <rPr>
@@ -885,70 +834,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE9" authorId="24" shapeId="0" xr:uid="{59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}">
+    <comment ref="AE9" authorId="4" shapeId="0" xr:uid="{2E436783-9E3B-49D7-BC62-F3C9428FF258}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="21" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
+    <comment ref="J10" authorId="17" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
       <text>
         <r>
           <rPr>
@@ -965,7 +868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V10" authorId="22" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
+    <comment ref="V10" authorId="18" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
       <text>
         <r>
           <rPr>
@@ -1028,7 +931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z10" authorId="23" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
+    <comment ref="Z10" authorId="19" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
       <text>
         <r>
           <rPr>
@@ -1045,70 +948,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE10" authorId="24" shapeId="0" xr:uid="{FD6930BF-6346-42D5-92D3-2FDEDA69C33D}">
+    <comment ref="AE10" authorId="4" shapeId="0" xr:uid="{A95393FA-918D-4430-8C62-F62A97C1C7BB}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="21" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
+    <comment ref="J11" authorId="17" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
       <text>
         <r>
           <rPr>
@@ -1125,7 +982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V11" authorId="22" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
+    <comment ref="V11" authorId="18" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
       <text>
         <r>
           <rPr>
@@ -1188,7 +1045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z11" authorId="23" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
+    <comment ref="Z11" authorId="19" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
       <text>
         <r>
           <rPr>
@@ -1205,70 +1062,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE11" authorId="24" shapeId="0" xr:uid="{125C2159-6A41-496C-957A-98F84A831963}">
+    <comment ref="AE11" authorId="4" shapeId="0" xr:uid="{31D77E5B-D9F8-4A52-A43B-E0E7FFA36C6F}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="21" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
+    <comment ref="J12" authorId="17" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
       <text>
         <r>
           <rPr>
@@ -1285,7 +1096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V12" authorId="22" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
+    <comment ref="V12" authorId="18" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
       <text>
         <r>
           <rPr>
@@ -1348,7 +1159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z12" authorId="23" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
+    <comment ref="Z12" authorId="19" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
       <text>
         <r>
           <rPr>
@@ -1365,70 +1176,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE12" authorId="24" shapeId="0" xr:uid="{A6C2F603-09FF-44E5-B2D4-65A036090CD5}">
+    <comment ref="AE12" authorId="4" shapeId="0" xr:uid="{BF4AAFF0-19FA-4D64-889A-0D7CFCA44AC8}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="21" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
+    <comment ref="J13" authorId="17" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
       <text>
         <r>
           <rPr>
@@ -1445,7 +1210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V13" authorId="22" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
+    <comment ref="V13" authorId="18" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
       <text>
         <r>
           <rPr>
@@ -1508,7 +1273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z13" authorId="23" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
+    <comment ref="Z13" authorId="19" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
       <text>
         <r>
           <rPr>
@@ -1525,66 +1290,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE13" authorId="24" shapeId="0" xr:uid="{B81F7C15-5FA5-4154-852C-1E0CA3F919A7}">
+    <comment ref="AE13" authorId="4" shapeId="0" xr:uid="{7B3299F8-219F-4A38-B351-3129FE5A3D30}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
         </r>
       </text>
     </comment>
@@ -1593,7 +1312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="190">
   <si>
     <t>variable_parameter</t>
   </si>
@@ -1682,9 +1401,6 @@
     <t>TOC_mol_m2_yr_precipitation</t>
   </si>
   <si>
-    <t>mol / m2 / year</t>
-  </si>
-  <si>
     <t>factor_how_many_times_Detritus_compared_to_TOC</t>
   </si>
   <si>
@@ -1764,9 +1480,6 @@
   </si>
   <si>
     <t>microbe_loss_factor_when_no_fauna</t>
-  </si>
-  <si>
-    <t>/(molCOD/L)/ day</t>
   </si>
   <si>
     <t>humic acid</t>
@@ -2119,9 +1832,6 @@
     <t>molar mass</t>
   </si>
   <si>
-    <t xml:space="preserve"> mol COD drymass_MO  mol COD acetate^-1</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2655,25 +2365,13 @@
     <t>recharge_fraction_of_precipitation</t>
   </si>
   <si>
-    <t xml:space="preserve">mol per  m^3 </t>
-  </si>
-  <si>
     <t>in Gerritse et al. (1992): 10.6 g- mol-1, i.e. 10.6/12 mol biomass / mol acetate -"Expressed as grams of cell carbon produced per mole of carbon substrate consumed." This was multiplied with 1.07 mol COD / mol biomass and divided by 2 mol COD / mol acetate</t>
   </si>
   <si>
     <t xml:space="preserve">fraction of detritus  becoming  BOC </t>
   </si>
   <si>
-    <t>mol COD/L at lab temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol COD/L </t>
-  </si>
-  <si>
     <t>2 mol COD / mol acetate. 64 g COD / 60 g acetate, i.e. 1.067 g COD / g acetate</t>
-  </si>
-  <si>
-    <t>per h micro g / L acetate</t>
   </si>
   <si>
     <t>microbial loss factor in scenarios where there is no fauna - i.e. cell respiration, grazing through the microbial loop, cell death etc.</t>
@@ -3391,28 +3089,28 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" t="s">
         <v>187</v>
       </c>
-      <c r="G1" t="s">
-        <v>194</v>
-      </c>
       <c r="H1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="L1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="M1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O1" t="s">
         <v>5</v>
@@ -3421,51 +3119,42 @@
         <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="W1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="X1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AF1" t="s">
         <v>184</v>
       </c>
-      <c r="Z1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB1" t="s">
+      <c r="AH1" t="s">
         <v>186</v>
       </c>
-      <c r="AE1" t="s">
-        <v>195</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>193</v>
-      </c>
       <c r="AJ1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:36">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" t="s">
-        <v>179</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -3476,26 +3165,11 @@
       <c r="S2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" t="s">
-        <v>80</v>
-      </c>
-      <c r="U2" t="s">
-        <v>182</v>
-      </c>
-      <c r="V2" t="s">
-        <v>183</v>
-      </c>
-      <c r="W2" t="s">
-        <v>185</v>
-      </c>
       <c r="AC2" t="s">
         <v>10</v>
       </c>
       <c r="AF2" t="s">
         <v>27</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:36">
@@ -3509,34 +3183,34 @@
         <v>4</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H3" t="s">
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
         <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>45</v>
       </c>
       <c r="N3" t="s">
         <v>24</v>
@@ -3551,7 +3225,7 @@
         <v>9</v>
       </c>
       <c r="R3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S3" t="s">
         <v>16</v>
@@ -3566,7 +3240,7 @@
         <v>20</v>
       </c>
       <c r="W3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>21</v>
@@ -3575,13 +3249,13 @@
         <v>22</v>
       </c>
       <c r="Z3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AB3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AC3" t="s">
         <v>11</v>
@@ -3599,13 +3273,13 @@
         <v>13</v>
       </c>
       <c r="AH3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AJ3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:36">
@@ -3623,14 +3297,14 @@
         <v>1419.5</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H4">
         <f t="shared" ref="H4:H13" si="1">203.5/1000</f>
         <v>0.20349999999999999</v>
       </c>
       <c r="I4">
-        <f>H4/F4*1000</f>
+        <f t="shared" ref="I4:I13" si="2">H4/F4*1000</f>
         <v>0.14336033814723495</v>
       </c>
       <c r="J4">
@@ -3661,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S4">
         <v>30</v>
@@ -3705,21 +3379,20 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>10*0.103714686</f>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF4">
         <v>1E-3</v>
       </c>
       <c r="AG4">
-        <f>0.000001</f>
-        <v>9.9999999999999995E-7</v>
+        <f>0.001</f>
+        <v>1E-3</v>
       </c>
       <c r="AH4">
         <v>1</v>
       </c>
       <c r="AI4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ4">
         <v>9.375E-2</v>
@@ -3740,18 +3413,18 @@
         <v>1419.5</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
       <c r="I5">
-        <f>H5/F5*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J9" si="2">I5*7.5</f>
+        <f t="shared" ref="J5:J9" si="3">I5*7.5</f>
         <v>1.0752025361042621</v>
       </c>
       <c r="K5">
@@ -3778,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S5">
         <v>30</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">10.6/12*1.07/2</f>
+        <f t="shared" ref="T5:T9" si="4">10.6/12*1.07/2</f>
         <v>0.47258333333333336</v>
       </c>
       <c r="U5">
@@ -3792,7 +3465,7 @@
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V5">
-        <f t="shared" ref="V5:V13" si="4">0.00000058</f>
+        <f t="shared" ref="V5:V13" si="5">0.00000058</f>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W5">
@@ -3815,28 +3488,27 @@
       <c r="AB5">
         <v>1E-4</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="21">
         <v>0</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <f t="shared" ref="AE5:AE13" si="5">10*0.103714686</f>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF5">
         <v>1E-3</v>
       </c>
       <c r="AG5">
-        <f t="shared" ref="AG5:AG13" si="6">0.000001</f>
-        <v>9.9999999999999995E-7</v>
+        <f t="shared" ref="AG5:AG13" si="6">0.001</f>
+        <v>1E-3</v>
       </c>
       <c r="AH5">
         <v>1</v>
       </c>
       <c r="AI5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ5">
         <v>9.375E-2</v>
@@ -3849,7 +3521,7 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="21">
         <v>1.5</v>
       </c>
       <c r="F6">
@@ -3857,18 +3529,18 @@
         <v>1419.5</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
       <c r="I6">
-        <f>H6/F6*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K6">
@@ -3895,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6">
         <v>30</v>
       </c>
       <c r="T6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.47258333333333336</v>
       </c>
       <c r="U6">
@@ -3909,7 +3581,7 @@
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W6">
@@ -3939,21 +3611,20 @@
         <v>0</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF6">
         <v>1E-3</v>
       </c>
       <c r="AG6">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH6">
         <v>1</v>
       </c>
       <c r="AI6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ6">
         <v>9.375E-2</v>
@@ -3966,7 +3637,7 @@
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="21">
         <v>1.5</v>
       </c>
       <c r="F7">
@@ -3974,18 +3645,18 @@
         <v>1419.5</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
       <c r="I7">
-        <f>H7/F7*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K7">
@@ -4012,13 +3683,13 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7">
         <v>30</v>
       </c>
       <c r="T7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.47258333333333336</v>
       </c>
       <c r="U7">
@@ -4026,7 +3697,7 @@
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W7">
@@ -4049,28 +3720,27 @@
       <c r="AB7">
         <v>1E-4</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="21">
         <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF7">
         <v>1E-3</v>
       </c>
       <c r="AG7">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH7">
         <v>1</v>
       </c>
       <c r="AI7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ7">
         <v>9.375E-2</v>
@@ -4083,7 +3753,7 @@
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="21">
         <v>3</v>
       </c>
       <c r="F8">
@@ -4091,18 +3761,18 @@
         <v>1419.5</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
         <v>0.20349999999999999</v>
       </c>
       <c r="I8">
-        <f>H8/F8*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K8">
@@ -4129,13 +3799,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S8">
         <v>30</v>
       </c>
       <c r="T8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.47258333333333336</v>
       </c>
       <c r="U8">
@@ -4143,7 +3813,7 @@
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W8">
@@ -4173,21 +3843,20 @@
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF8">
         <v>1E-3</v>
       </c>
       <c r="AG8">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH8">
         <v>1</v>
       </c>
       <c r="AI8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ8">
         <v>9.375E-2</v>
@@ -4200,7 +3869,7 @@
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="21">
         <v>3</v>
       </c>
       <c r="F9">
@@ -4215,11 +3884,11 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I9">
-        <f>H9/F9*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K9">
@@ -4246,13 +3915,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S9">
         <v>30</v>
       </c>
       <c r="T9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.47258333333333336</v>
       </c>
       <c r="U9">
@@ -4260,7 +3929,7 @@
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W9">
@@ -4283,28 +3952,27 @@
       <c r="AB9">
         <v>1E-4</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="21">
         <v>0</v>
       </c>
       <c r="AD9">
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF9">
         <v>1E-3</v>
       </c>
       <c r="AG9">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH9">
         <v>1</v>
       </c>
       <c r="AI9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ9">
         <v>9.375E-2</v>
@@ -4332,7 +4000,7 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I10">
-        <f>H10/F10*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J10">
@@ -4363,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S10">
         <v>30</v>
@@ -4372,11 +4040,11 @@
         <v>1E-3</v>
       </c>
       <c r="U10">
-        <f t="shared" ref="U10:U11" si="15">4.3 /1000000 *1.07</f>
+        <f t="shared" ref="U10:U13" si="15">4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W10">
@@ -4406,21 +4074,20 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF10">
         <v>1E-3</v>
       </c>
       <c r="AG10">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH10">
         <v>1</v>
       </c>
       <c r="AI10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ10">
         <v>9.375E-2</v>
@@ -4448,7 +4115,7 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I11">
-        <f>H11/F11*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J11">
@@ -4479,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S11">
         <v>30</v>
@@ -4492,7 +4159,7 @@
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W11">
@@ -4522,21 +4189,20 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF11">
         <v>1E-3</v>
       </c>
       <c r="AG11">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH11">
         <v>1</v>
       </c>
       <c r="AI11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ11">
         <v>9.375E-2</v>
@@ -4564,7 +4230,7 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I12">
-        <f>H12/F12*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J12">
@@ -4582,8 +4248,8 @@
         <f>L12*J12</f>
         <v>10.752025361042621</v>
       </c>
-      <c r="N12">
-        <v>1E-4</v>
+      <c r="N12" s="21">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -4595,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S12">
         <v>30</v>
@@ -4604,11 +4270,12 @@
         <f t="shared" ref="T12:T13" si="18">10.6/12*1.07/2</f>
         <v>0.47258333333333336</v>
       </c>
-      <c r="U12" s="21">
-        <v>1.0000000000000001E-5</v>
+      <c r="U12">
+        <f t="shared" si="15"/>
+        <v>4.6009999999999997E-6</v>
       </c>
       <c r="V12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W12">
@@ -4638,21 +4305,20 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF12">
         <v>1E-3</v>
       </c>
       <c r="AG12">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH12">
         <v>1</v>
       </c>
       <c r="AI12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ12">
         <v>9.375E-2</v>
@@ -4680,7 +4346,7 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I13">
-        <f>H13/F13*1000</f>
+        <f t="shared" si="2"/>
         <v>0.14336033814723495</v>
       </c>
       <c r="J13">
@@ -4698,8 +4364,8 @@
         <f>L13*J13</f>
         <v>10.752025361042621</v>
       </c>
-      <c r="N13">
-        <v>1E-4</v>
+      <c r="N13" s="21">
+        <v>0.01</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -4711,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S13">
         <v>30</v>
@@ -4720,11 +4386,12 @@
         <f t="shared" si="18"/>
         <v>0.47258333333333336</v>
       </c>
-      <c r="U13" s="21">
-        <v>9.9999999999999995E-8</v>
+      <c r="U13">
+        <f t="shared" si="15"/>
+        <v>4.6009999999999997E-6</v>
       </c>
       <c r="V13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7999999999999995E-7</v>
       </c>
       <c r="W13">
@@ -4754,21 +4421,20 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="5"/>
-        <v>1.03714686</v>
+        <v>0.02</v>
       </c>
       <c r="AF13">
         <v>1E-3</v>
       </c>
       <c r="AG13">
         <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
+        <v>1E-3</v>
       </c>
       <c r="AH13">
         <v>1</v>
       </c>
       <c r="AI13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AJ13">
         <v>9.375E-2</v>
@@ -4793,7 +4459,7 @@
   <sheetData>
     <row r="1" spans="2:21">
       <c r="B1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="2:21">
@@ -4876,38 +4542,38 @@
     </row>
     <row r="16" spans="2:21">
       <c r="L16" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="12:20">
       <c r="L17" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N17" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17" t="s">
+        <v>37</v>
+      </c>
+      <c r="P17" t="s">
         <v>34</v>
       </c>
-      <c r="O17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>35</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>36</v>
       </c>
-      <c r="R17" t="s">
-        <v>37</v>
-      </c>
       <c r="T17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="12:20">
       <c r="L18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -4928,12 +4594,12 @@
     </row>
     <row r="19" spans="12:20">
       <c r="L19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="12:20">
       <c r="L20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="12:20">
@@ -4942,43 +4608,43 @@
         <v>227</v>
       </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="12:20">
       <c r="L22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="12:20">
       <c r="L25" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O25" t="s">
+        <v>37</v>
+      </c>
+      <c r="P25" t="s">
         <v>34</v>
       </c>
-      <c r="O25" t="s">
-        <v>38</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>35</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>36</v>
       </c>
-      <c r="R25" t="s">
-        <v>37</v>
-      </c>
       <c r="T25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="12:20">
       <c r="L26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O26">
         <v>2</v>
@@ -5002,53 +4668,53 @@
         <v>60</v>
       </c>
       <c r="M27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="12:20">
       <c r="L28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="12:20">
       <c r="L31" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="12:20" ht="18">
       <c r="L32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="10:20">
       <c r="L33" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N33" t="s">
+        <v>33</v>
+      </c>
+      <c r="O33" t="s">
+        <v>37</v>
+      </c>
+      <c r="P33" t="s">
         <v>34</v>
       </c>
-      <c r="O33" t="s">
-        <v>38</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>35</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>36</v>
       </c>
-      <c r="R33" t="s">
-        <v>37</v>
-      </c>
       <c r="T33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="10:20">
       <c r="L34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -5071,7 +4737,7 @@
       <c r="J35" s="11"/>
       <c r="K35" s="10"/>
       <c r="L35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="10:20">
@@ -5089,7 +4755,7 @@
     </row>
     <row r="40" spans="10:20">
       <c r="M40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="10:20">
@@ -5097,25 +4763,25 @@
         <v>2.6</v>
       </c>
       <c r="N41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P41">
         <v>2.6</v>
       </c>
       <c r="Q41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="10:20">
       <c r="L42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M42">
         <f>12+1.8+0.5*16+0.2*14</f>
         <v>24.6</v>
       </c>
       <c r="N42" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="10:20">
@@ -5126,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="3:14">
@@ -5135,10 +4801,10 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="M51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="3:14">
@@ -5147,7 +4813,7 @@
         <v>2.032520325203252E-10</v>
       </c>
       <c r="M54" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="3:14">
@@ -5164,81 +4830,81 @@
     </row>
     <row r="58" spans="3:14">
       <c r="L58" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="3:14" ht="18">
       <c r="L59" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="3:14">
       <c r="C60" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M60">
         <f>5*12+7+2*16+14</f>
         <v>113</v>
       </c>
       <c r="N60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="3:14">
       <c r="D61" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E61" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L61" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="3:14">
       <c r="C62" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D62">
         <v>7.5</v>
       </c>
       <c r="E62" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="3:14">
       <c r="C63" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D63">
         <v>5.9</v>
       </c>
       <c r="E63" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L63" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="3:14">
       <c r="C64" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D64" s="13">
         <f>D62-D63</f>
         <v>1.5999999999999996</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F64" s="13"/>
       <c r="K64">
@@ -5246,117 +4912,117 @@
         <v>4.25</v>
       </c>
       <c r="L64" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="3:13">
       <c r="C65" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D65" s="13">
         <f>D62+D63</f>
         <v>13.4</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F65" s="13"/>
       <c r="L65" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="3:13">
       <c r="C66" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D66">
         <f>D62/227.172/1000</f>
         <v>3.3014632084940045E-5</v>
       </c>
       <c r="E66" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L66">
         <f>4.25*32</f>
         <v>136</v>
       </c>
       <c r="M66" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="3:13">
       <c r="C67" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D67">
         <f>D63/227.172/1000</f>
         <v>2.5971510573486172E-5</v>
       </c>
       <c r="E67" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L67">
         <f>L66/M60</f>
         <v>1.2035398230088497</v>
       </c>
       <c r="M67" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="3:13">
       <c r="C68" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D68">
         <f>D66*24.6</f>
         <v>8.1215994928952515E-4</v>
       </c>
       <c r="E68" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L68" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="3:13">
       <c r="C69" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D69">
         <f>D67*24.6</f>
         <v>6.388991601077599E-4</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="3:13">
       <c r="C70" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D70">
         <f>D68*1.075/1.05</f>
         <v>8.3149709093927569E-4</v>
       </c>
       <c r="E70" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="3:13">
       <c r="C71" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D71">
         <f>D69*1.075/1.05</f>
         <v>6.5411104487223025E-4</v>
       </c>
       <c r="E71" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="3:13">
       <c r="C75" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="3:13">
@@ -5364,7 +5030,7 @@
         <v>0.33</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="3:13">
@@ -5372,7 +5038,7 @@
         <v>0.73</v>
       </c>
       <c r="E77" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="3:13">
@@ -5381,7 +5047,7 @@
         <v>3.3000000000000002E-7</v>
       </c>
       <c r="E78" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="3:13">
@@ -5390,7 +5056,7 @@
         <v>7.3E-7</v>
       </c>
       <c r="E79" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="3:13">
@@ -5399,7 +5065,7 @@
         <v>2.7500000000000001E-8</v>
       </c>
       <c r="E80" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="4:12">
@@ -5408,7 +5074,7 @@
         <v>6.0833333333333329E-8</v>
       </c>
       <c r="E81" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="4:12">
@@ -5417,7 +5083,7 @@
         <v>5.5000000000000014E-3</v>
       </c>
       <c r="E82" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="4:12">
@@ -5426,7 +5092,7 @@
         <v>1.2166666666666666E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="4:12">
@@ -5435,7 +5101,7 @@
         <v>0.13530000000000003</v>
       </c>
       <c r="E84" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="4:12">
@@ -5444,7 +5110,7 @@
         <v>0.29930000000000001</v>
       </c>
       <c r="E85" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="4:12">
@@ -5453,7 +5119,7 @@
         <v>0.12885714285714289</v>
       </c>
       <c r="E86" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="4:12">
@@ -5462,7 +5128,7 @@
         <v>0.28504761904761905</v>
       </c>
       <c r="E87" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="4:12">
@@ -5471,10 +5137,10 @@
         <v>8.4242681454371637E-2</v>
       </c>
       <c r="E89" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="4:12">
@@ -5482,13 +5148,13 @@
         <v>6.905E-6</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K90">
         <v>0.35</v>
       </c>
       <c r="L90" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="4:12">
@@ -5497,14 +5163,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E91" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K91">
         <f>K90/1000000/24.6</f>
         <v>1.4227642276422762E-8</v>
       </c>
       <c r="L91" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="4:12">
@@ -5513,14 +5179,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E92" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K92">
         <f>K91*1.05</f>
         <v>1.4939024390243901E-8</v>
       </c>
       <c r="L92" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93" spans="4:12">
@@ -5529,7 +5195,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L93" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" spans="4:12">
@@ -5538,12 +5204,12 @@
         <v>1.4939024390243901E-3</v>
       </c>
       <c r="L94" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="4:12">
       <c r="E96" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" spans="4:14">
@@ -5551,7 +5217,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="4:14">
@@ -5559,13 +5225,13 @@
         <v>9.09</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F98" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L98" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="4:14">
@@ -5573,20 +5239,20 @@
         <v>7.58</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F99" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L99">
         <f>AVERAGE(D127, D86:D87,D70)</f>
         <v>0.10371468607138892</v>
       </c>
       <c r="M99" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N99" s="16" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100" spans="4:14">
@@ -5594,13 +5260,13 @@
         <v>7.96</v>
       </c>
       <c r="E100" t="s">
+        <v>121</v>
+      </c>
+      <c r="F100" t="s">
         <v>124</v>
       </c>
-      <c r="F100" t="s">
-        <v>127</v>
-      </c>
       <c r="N100" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="101" spans="4:14">
@@ -5608,10 +5274,10 @@
         <v>6.52</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F101" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="4:14">
@@ -5619,10 +5285,10 @@
         <v>4.71</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F102" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H102">
         <f>AVERAGE(D102:D105)</f>
@@ -5634,10 +5300,10 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F103" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="4:14">
@@ -5645,10 +5311,10 @@
         <v>4.18</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F104" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="4:14">
@@ -5656,10 +5322,10 @@
         <v>4.13</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F105" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="4:14">
@@ -5667,7 +5333,7 @@
         <v>4.3</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107" spans="4:14">
@@ -5675,7 +5341,7 @@
         <v>0.5</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="4:14">
@@ -5683,7 +5349,7 @@
         <v>14.9</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="109" spans="4:14">
@@ -5691,7 +5357,7 @@
         <v>1.9</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="4:14">
@@ -5699,7 +5365,7 @@
         <v>12.4</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="4:14">
@@ -5707,7 +5373,7 @@
         <v>1.2</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" spans="4:14">
@@ -5715,7 +5381,7 @@
         <v>0.01</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="4:5">
@@ -5723,7 +5389,7 @@
         <v>8.1</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="4:5">
@@ -5731,12 +5397,12 @@
         <v>0.15336312500000002</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="4:5">
       <c r="E115" s="17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="4:5">
@@ -5745,7 +5411,7 @@
         <v>8.3333333333333344E-7</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117" spans="4:5">
@@ -5754,7 +5420,7 @@
         <v>6.7499999999999993E-4</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="118" spans="4:5">
@@ -5763,7 +5429,7 @@
         <v>1.2780260416666668E-5</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="119" spans="4:5">
@@ -5772,7 +5438,7 @@
         <v>1.9190174630589144E-7</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="4:5">
@@ -5781,7 +5447,7 @@
         <v>1.5544041450777204E-4</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" spans="4:5">
@@ -5790,7 +5456,7 @@
         <v>2.9430651506428716E-6</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="122" spans="4:5">
@@ -5799,7 +5465,7 @@
         <v>7.8008839961744482E-6</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="123" spans="4:5">
@@ -5808,7 +5474,7 @@
         <v>6.3187160369013026E-3</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="124" spans="4:5">
@@ -5817,7 +5483,7 @@
         <v>1.1963679474158013E-4</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="4:5">
@@ -5826,7 +5492,7 @@
         <v>7.9866193294166962E-6</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="126" spans="4:5">
@@ -5835,7 +5501,7 @@
         <v>6.4691616568275231E-3</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="127" spans="4:5">
@@ -5844,12 +5510,12 @@
         <v>1.224852898544749E-4</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="130" spans="4:6" ht="198">
       <c r="D130" s="20" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="131" spans="4:6">
@@ -5858,10 +5524,10 @@
         <v>1.6000000000000003E-5</v>
       </c>
       <c r="E131" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F131" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="132" spans="4:6">
@@ -5870,10 +5536,10 @@
         <v>4.5714285714285719E-6</v>
       </c>
       <c r="E132" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F132" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="133" spans="4:6">
@@ -5881,10 +5547,10 @@
         <v>630000</v>
       </c>
       <c r="E133" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F133" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134" spans="4:6">
@@ -5893,10 +5559,10 @@
         <v>6.3E+17</v>
       </c>
       <c r="E134" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F134" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="4:6">
@@ -5905,10 +5571,10 @@
         <v>2880000000000.0005</v>
       </c>
       <c r="E135" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F135" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="136" spans="4:6">
@@ -5917,10 +5583,10 @@
         <v>227</v>
       </c>
       <c r="E136" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F136" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="137" spans="4:6">
@@ -5929,10 +5595,10 @@
         <v>653760000000000.13</v>
       </c>
       <c r="E137" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F137" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="138" spans="4:6">
@@ -5941,10 +5607,10 @@
         <v>653760000000.00012</v>
       </c>
       <c r="E138" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F138" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="139" spans="4:6">
@@ -5953,10 +5619,10 @@
         <v>653760000.00000012</v>
       </c>
       <c r="E139" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F139" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9997450B-502C-46B8-9820-CCAA9DD35877}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920A823B-A0F9-467B-ABDD-6094D82855CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
@@ -424,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE5" authorId="4" shapeId="0" xr:uid="{3A4E7E2B-C45D-41E9-96C1-3B0C321FF477}">
+    <comment ref="AE5" authorId="4" shapeId="0" xr:uid="{853BCBCA-AD94-4092-B9D5-CDE911D53FC2}">
       <text>
         <r>
           <rPr>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE6" authorId="4" shapeId="0" xr:uid="{81C33CF6-277A-4464-8765-7CFDC40903D9}">
+    <comment ref="AE6" authorId="4" shapeId="0" xr:uid="{51AED2A8-D3B7-403D-AA5A-200DCAABACFA}">
       <text>
         <r>
           <rPr>
@@ -606,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE7" authorId="4" shapeId="0" xr:uid="{F5DBD1C4-1855-49B5-A8A2-512AEE391C65}">
+    <comment ref="AE7" authorId="4" shapeId="0" xr:uid="{336D7F98-AD70-4487-9E19-A2872968D1C6}">
       <text>
         <r>
           <rPr>
@@ -720,7 +720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE8" authorId="4" shapeId="0" xr:uid="{45A9C127-CEF7-4D99-93CE-A916236D9D99}">
+    <comment ref="AE8" authorId="4" shapeId="0" xr:uid="{2A45CBFD-6121-4554-8977-78E204540AE9}">
       <text>
         <r>
           <rPr>
@@ -834,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE9" authorId="4" shapeId="0" xr:uid="{2E436783-9E3B-49D7-BC62-F3C9428FF258}">
+    <comment ref="AE9" authorId="4" shapeId="0" xr:uid="{AA8D6C3D-3E14-4946-A46D-8747516AE283}">
       <text>
         <r>
           <rPr>
@@ -948,7 +948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE10" authorId="4" shapeId="0" xr:uid="{A95393FA-918D-4430-8C62-F62A97C1C7BB}">
+    <comment ref="AE10" authorId="4" shapeId="0" xr:uid="{86F3F138-07CF-4120-B34C-9F8AF0FDCE5B}">
       <text>
         <r>
           <rPr>
@@ -1062,7 +1062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE11" authorId="4" shapeId="0" xr:uid="{31D77E5B-D9F8-4A52-A43B-E0E7FFA36C6F}">
+    <comment ref="AE11" authorId="4" shapeId="0" xr:uid="{24967105-65BC-4B43-B982-22847566800B}">
       <text>
         <r>
           <rPr>
@@ -1176,7 +1176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE12" authorId="4" shapeId="0" xr:uid="{BF4AAFF0-19FA-4D64-889A-0D7CFCA44AC8}">
+    <comment ref="AE12" authorId="4" shapeId="0" xr:uid="{DE302AD6-DC40-4C0E-98E6-EC607558285A}">
       <text>
         <r>
           <rPr>
@@ -1290,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE13" authorId="4" shapeId="0" xr:uid="{7B3299F8-219F-4A38-B351-3129FE5A3D30}">
+    <comment ref="AE13" authorId="4" shapeId="0" xr:uid="{6E879F82-2B4B-45FB-AB54-CD13EDAE8F66}">
       <text>
         <r>
           <rPr>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF4">
         <v>1E-3</v>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF5">
         <v>1E-3</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF6">
         <v>1E-3</v>
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF7">
         <v>1E-3</v>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF8">
         <v>1E-3</v>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF9">
         <v>1E-3</v>
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF10">
         <v>1E-3</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF11">
         <v>1E-3</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF12">
         <v>1E-3</v>
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="AF13">
         <v>1E-3</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920A823B-A0F9-467B-ABDD-6094D82855CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23170355-5709-4846-A6D2-985693089006}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="calculating_COD" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$3:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$3:$AI$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD3" authorId="0" shapeId="0" xr:uid="{C3505123-F90F-DE41-BEE8-86A5DB659096}">
+    <comment ref="AC3" authorId="0" shapeId="0" xr:uid="{C3505123-F90F-DE41-BEE8-86A5DB659096}">
       <text>
         <r>
           <rPr>
@@ -247,7 +247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z4" authorId="3" shapeId="0" xr:uid="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
+    <comment ref="Y4" authorId="3" shapeId="0" xr:uid="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
       <text>
         <r>
           <rPr>
@@ -310,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE4" authorId="4" shapeId="0" xr:uid="{D83D8722-287D-8543-91DC-DFD968583D4B}">
+    <comment ref="AD4" authorId="4" shapeId="0" xr:uid="{D83D8722-287D-8543-91DC-DFD968583D4B}">
       <text>
         <r>
           <rPr>
@@ -323,7 +323,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -407,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z5" authorId="7" shapeId="0" xr:uid="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
+    <comment ref="Y5" authorId="7" shapeId="0" xr:uid="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
       <text>
         <r>
           <rPr>
@@ -424,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE5" authorId="4" shapeId="0" xr:uid="{853BCBCA-AD94-4092-B9D5-CDE911D53FC2}">
+    <comment ref="AD5" authorId="4" shapeId="0" xr:uid="{16668028-E470-49D8-A575-5BF14B51E0D7}">
       <text>
         <r>
           <rPr>
@@ -437,7 +437,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -521,7 +521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z6" authorId="10" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
+    <comment ref="Y6" authorId="10" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
       <text>
         <r>
           <rPr>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE6" authorId="4" shapeId="0" xr:uid="{51AED2A8-D3B7-403D-AA5A-200DCAABACFA}">
+    <comment ref="AD6" authorId="4" shapeId="0" xr:uid="{2C3E63E2-3AE0-4A5B-8C7D-9BF28330D619}">
       <text>
         <r>
           <rPr>
@@ -551,7 +551,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -589,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z7" authorId="13" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
+    <comment ref="Y7" authorId="13" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
       <text>
         <r>
           <rPr>
@@ -606,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE7" authorId="4" shapeId="0" xr:uid="{336D7F98-AD70-4487-9E19-A2872968D1C6}">
+    <comment ref="AD7" authorId="4" shapeId="0" xr:uid="{52E6596C-BF01-40FE-80EF-E81EF72B1B0A}">
       <text>
         <r>
           <rPr>
@@ -619,7 +619,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -703,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z8" authorId="16" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
+    <comment ref="Y8" authorId="16" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
       <text>
         <r>
           <rPr>
@@ -720,7 +720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE8" authorId="4" shapeId="0" xr:uid="{2A45CBFD-6121-4554-8977-78E204540AE9}">
+    <comment ref="AD8" authorId="4" shapeId="0" xr:uid="{92E5DB6E-68AE-4BE9-AC60-965E4EFEF9C9}">
       <text>
         <r>
           <rPr>
@@ -733,7 +733,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -817,7 +817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z9" authorId="19" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
+    <comment ref="Y9" authorId="19" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
       <text>
         <r>
           <rPr>
@@ -834,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE9" authorId="4" shapeId="0" xr:uid="{AA8D6C3D-3E14-4946-A46D-8747516AE283}">
+    <comment ref="AD9" authorId="4" shapeId="0" xr:uid="{5B2AB557-5C4D-4A18-B601-D1F593004EA2}">
       <text>
         <r>
           <rPr>
@@ -847,7 +847,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -931,7 +931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z10" authorId="19" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
+    <comment ref="Y10" authorId="19" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
       <text>
         <r>
           <rPr>
@@ -948,7 +948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE10" authorId="4" shapeId="0" xr:uid="{86F3F138-07CF-4120-B34C-9F8AF0FDCE5B}">
+    <comment ref="AD10" authorId="4" shapeId="0" xr:uid="{3A5D2B68-C202-47CB-8961-7FC8DDCB5D87}">
       <text>
         <r>
           <rPr>
@@ -961,7 +961,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -1045,7 +1045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z11" authorId="19" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
+    <comment ref="Y11" authorId="19" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
       <text>
         <r>
           <rPr>
@@ -1062,7 +1062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE11" authorId="4" shapeId="0" xr:uid="{24967105-65BC-4B43-B982-22847566800B}">
+    <comment ref="AD11" authorId="4" shapeId="0" xr:uid="{48DA997C-8DFD-4B73-9E86-327CAC4DFDC5}">
       <text>
         <r>
           <rPr>
@@ -1075,7 +1075,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -1159,7 +1159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z12" authorId="19" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
+    <comment ref="Y12" authorId="19" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
       <text>
         <r>
           <rPr>
@@ -1176,7 +1176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE12" authorId="4" shapeId="0" xr:uid="{DE302AD6-DC40-4C0E-98E6-EC607558285A}">
+    <comment ref="AD12" authorId="4" shapeId="0" xr:uid="{155DF592-3843-4EA8-9AB8-E5135E1BAF92}">
       <text>
         <r>
           <rPr>
@@ -1189,7 +1189,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -1273,7 +1273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z13" authorId="19" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
+    <comment ref="Y13" authorId="19" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
       <text>
         <r>
           <rPr>
@@ -1290,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE13" authorId="4" shapeId="0" xr:uid="{6E879F82-2B4B-45FB-AB54-CD13EDAE8F66}">
+    <comment ref="AD13" authorId="4" shapeId="0" xr:uid="{B66749DF-A4F3-46FC-B53B-BE6D26C8C927}">
       <text>
         <r>
           <rPr>
@@ -1303,7 +1303,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
         </r>
       </text>
     </comment>
@@ -1312,7 +1312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="188">
   <si>
     <t>variable_parameter</t>
   </si>
@@ -1375,9 +1375,6 @@
   </si>
   <si>
     <t>K_MO_at_temp</t>
-  </si>
-  <si>
-    <t>rMO_COD_uptake_h_at_lab_temperature</t>
   </si>
   <si>
     <t>rMO_COD_uptake_per_day_at_lab_temperature</t>
@@ -2371,9 +2368,6 @@
     <t xml:space="preserve">fraction of detritus  becoming  BOC </t>
   </si>
   <si>
-    <t>2 mol COD / mol acetate. 64 g COD / 60 g acetate, i.e. 1.067 g COD / g acetate</t>
-  </si>
-  <si>
     <t>microbial loss factor in scenarios where there is no fauna - i.e. cell respiration, grazing through the microbial loop, cell death etc.</t>
   </si>
   <si>
@@ -2386,9 +2380,6 @@
     <t>the factor how many times of TOC there is carbon bound in detritus; assuming that through soil passage, the TOC from precipitation is degraded, but a lot more detritus is mobilised</t>
   </si>
   <si>
-    <t>rate constant for bacterial uptake and oxidation of acetate Gerritse et al. (1992), assuming COD can be degraded like acetate, which is an error-prone assumption</t>
-  </si>
-  <si>
     <t>excretion rate of fauna; constant rate; excretion is biodegradable organic carbon (BOC) and added to that pool</t>
   </si>
   <si>
@@ -2405,6 +2396,9 @@
   </si>
   <si>
     <t>100% survival at 12 degrees, between 50 and 100% at 16 degrees, between 0 and50% at 20 degrees (Brielmann 2011). Assuming that half of the fauna population behaves like amphipods and half like asellids, 100% survival at 12 degrees, (75% survival at 16 degrees,) 25 % at 20 degrees. Taking the endpoint 20 degrees, 0.25 of the population survives after an increase by 8 degrees. This means that 0.75 have died. Thus , for each degree of increase, 0.75/8 = 0.09375 , roughly 1 % of the individuals die.    above or below 12 degree</t>
+  </si>
+  <si>
+    <t>rate constant per hour for bacterial uptake and oxidation of acetate Gerritse et al. (1992), assuming COD can be degraded like acetate, which is an error-prone assumption</t>
   </si>
 </sst>
 </file>
@@ -3073,7 +3067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}">
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -3081,36 +3075,36 @@
     <col min="11" max="11" width="11.19921875" customWidth="1"/>
     <col min="13" max="13" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" t="s">
+        <v>179</v>
+      </c>
+      <c r="L1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H1" t="s">
-        <v>181</v>
-      </c>
-      <c r="L1" t="s">
-        <v>182</v>
-      </c>
       <c r="M1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O1" t="s">
         <v>5</v>
@@ -3119,45 +3113,42 @@
         <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W1" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG1" t="s">
         <v>183</v>
       </c>
-      <c r="X1" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>188</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>184</v>
-      </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>186</v>
       </c>
-      <c r="AJ1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36">
+    </row>
+    <row r="2" spans="1:35">
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
         <v>8</v>
@@ -3165,14 +3156,14 @@
       <c r="S2" t="s">
         <v>18</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AB2" t="s">
         <v>10</v>
       </c>
-      <c r="AF2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
+      <c r="AE2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3183,37 +3174,37 @@
         <v>4</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>43</v>
       </c>
-      <c r="K3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O3" t="s">
         <v>6</v>
@@ -3225,7 +3216,7 @@
         <v>9</v>
       </c>
       <c r="R3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S3" t="s">
         <v>16</v>
@@ -3240,49 +3231,46 @@
         <v>20</v>
       </c>
       <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X3" t="s">
         <v>21</v>
       </c>
       <c r="Y3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD3" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA3" t="s">
+      <c r="AE3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG3" t="s">
         <v>50</v>
       </c>
-      <c r="AB3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>13</v>
-      </c>
       <c r="AH3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AI3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35">
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -3335,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S4">
         <v>30</v>
@@ -3355,50 +3343,47 @@
       <c r="W4">
         <v>0.43</v>
       </c>
-      <c r="X4" s="4">
-        <f>W4*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X4">
+        <f>W4 *24</f>
+        <v>10.32</v>
       </c>
       <c r="Y4">
-        <f>X4 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA4">
+        <v>1E-4</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>2E-3</v>
+      </c>
+      <c r="AE4">
+        <f>0.0001</f>
         <v>1E-4</v>
       </c>
-      <c r="AC4">
+      <c r="AF4">
+        <f>0.0001</f>
+        <v>1E-4</v>
+      </c>
+      <c r="AG4">
         <v>1</v>
       </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>2E-3</v>
-      </c>
-      <c r="AF4">
-        <v>1E-3</v>
-      </c>
-      <c r="AG4">
-        <f>0.001</f>
-        <v>1E-3</v>
-      </c>
-      <c r="AH4">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ4">
+      <c r="AH4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI4">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:35">
       <c r="B5">
         <v>2</v>
       </c>
@@ -3451,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S5">
         <v>30</v>
@@ -3471,50 +3456,47 @@
       <c r="W5">
         <v>0.43</v>
       </c>
-      <c r="X5" s="4">
-        <f>W5*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X5">
+        <f t="shared" ref="X5:X13" si="6">W5 *24</f>
+        <v>10.32</v>
       </c>
       <c r="Y5">
-        <f>X5 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z5">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA5">
+        <v>1E-4</v>
+      </c>
+      <c r="AB5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>2E-3</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" ref="AE5:AF13" si="7">0.0001</f>
+        <v>1E-4</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG5">
         <v>1</v>
       </c>
-      <c r="AB5">
-        <v>1E-4</v>
-      </c>
-      <c r="AC5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>2E-3</v>
-      </c>
-      <c r="AF5">
-        <v>1E-3</v>
-      </c>
-      <c r="AG5">
-        <f t="shared" ref="AG5:AG13" si="6">0.001</f>
-        <v>1E-3</v>
-      </c>
-      <c r="AH5">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ5">
+      <c r="AH5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI5">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:35">
       <c r="B6">
         <v>3</v>
       </c>
@@ -3544,14 +3526,14 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K9" si="7">J6/1000</f>
+        <f t="shared" ref="K6:K9" si="8">J6/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L6" s="4">
         <v>10</v>
       </c>
       <c r="M6">
-        <f t="shared" ref="M6" si="8">L6*J6</f>
+        <f t="shared" ref="M6" si="9">L6*J6</f>
         <v>10.752025361042621</v>
       </c>
       <c r="N6">
@@ -3567,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S6">
         <v>30</v>
@@ -3577,7 +3559,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U9" si="9">4.3 /1000000 *1.07</f>
+        <f t="shared" ref="U6:U9" si="10">4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V6">
@@ -3587,50 +3569,47 @@
       <c r="W6">
         <v>0.43</v>
       </c>
-      <c r="X6" s="4">
-        <f t="shared" ref="X6:X8" si="10">W6*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X6">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y6">
-        <f t="shared" ref="Y6:Y8" si="11">X6 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z6">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA6">
+        <v>1E-4</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
-      <c r="AB6">
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>2E-3</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="7"/>
         <v>1E-4</v>
       </c>
-      <c r="AC6">
+      <c r="AF6">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG6">
         <v>1</v>
       </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>2E-3</v>
-      </c>
-      <c r="AF6">
-        <v>1E-3</v>
-      </c>
-      <c r="AG6">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ6">
+      <c r="AH6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI6">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:35">
       <c r="B7">
         <v>4</v>
       </c>
@@ -3660,7 +3639,7 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L7" s="4">
@@ -3683,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S7">
         <v>30</v>
@@ -3693,7 +3672,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V7">
@@ -3703,50 +3682,47 @@
       <c r="W7">
         <v>0.43</v>
       </c>
-      <c r="X7" s="4">
-        <f t="shared" si="10"/>
-        <v>0.45838000000000001</v>
+      <c r="X7">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="11"/>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z7">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA7">
+        <v>1E-4</v>
+      </c>
+      <c r="AB7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>2E-3</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG7">
         <v>1</v>
       </c>
-      <c r="AB7">
-        <v>1E-4</v>
-      </c>
-      <c r="AC7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>2E-3</v>
-      </c>
-      <c r="AF7">
-        <v>1E-3</v>
-      </c>
-      <c r="AG7">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH7">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ7">
+      <c r="AH7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI7">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:35">
       <c r="B8">
         <v>5</v>
       </c>
@@ -3776,14 +3752,14 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L8" s="4">
         <v>10</v>
       </c>
       <c r="M8">
-        <f t="shared" ref="M8" si="12">L8*J8</f>
+        <f t="shared" ref="M8" si="11">L8*J8</f>
         <v>10.752025361042621</v>
       </c>
       <c r="N8">
@@ -3799,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S8">
         <v>30</v>
@@ -3809,7 +3785,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V8">
@@ -3819,50 +3795,47 @@
       <c r="W8">
         <v>0.43</v>
       </c>
-      <c r="X8" s="4">
-        <f t="shared" si="10"/>
-        <v>0.45838000000000001</v>
+      <c r="X8">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="11"/>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z8">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA8">
+        <v>1E-4</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
-      <c r="AB8">
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>2E-3</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="7"/>
         <v>1E-4</v>
       </c>
-      <c r="AC8">
+      <c r="AF8">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG8">
         <v>1</v>
       </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>2E-3</v>
-      </c>
-      <c r="AF8">
-        <v>1E-3</v>
-      </c>
-      <c r="AG8">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH8">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ8">
+      <c r="AH8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI8">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:35">
       <c r="B9">
         <v>6</v>
       </c>
@@ -3892,7 +3865,7 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L9" s="4">
@@ -3915,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S9">
         <v>30</v>
@@ -3925,7 +3898,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V9">
@@ -3935,50 +3908,47 @@
       <c r="W9">
         <v>0.43</v>
       </c>
-      <c r="X9" s="4">
-        <f>W9*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X9">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y9">
-        <f>X9 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z9">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA9">
+        <v>1E-4</v>
+      </c>
+      <c r="AB9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>2E-3</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG9">
         <v>1</v>
       </c>
-      <c r="AB9">
-        <v>1E-4</v>
-      </c>
-      <c r="AC9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>2E-3</v>
-      </c>
-      <c r="AF9">
-        <v>1E-3</v>
-      </c>
-      <c r="AG9">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH9">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ9">
+      <c r="AH9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI9">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:35">
       <c r="B10">
         <v>7</v>
       </c>
@@ -4004,11 +3974,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J10">
-        <f t="shared" ref="J10:J11" si="13">I10*7.5</f>
+        <f t="shared" ref="J10:J11" si="12">I10*7.5</f>
         <v>1.0752025361042621</v>
       </c>
       <c r="K10">
-        <f t="shared" ref="K10:K11" si="14">J10/1000</f>
+        <f t="shared" ref="K10:K11" si="13">J10/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L10" s="4">
@@ -4031,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S10">
         <v>30</v>
@@ -4040,7 +4010,7 @@
         <v>1E-3</v>
       </c>
       <c r="U10">
-        <f t="shared" ref="U10:U13" si="15">4.3 /1000000 *1.07</f>
+        <f t="shared" ref="U10:U13" si="14">4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V10">
@@ -4050,50 +4020,47 @@
       <c r="W10">
         <v>0.43</v>
       </c>
-      <c r="X10" s="4">
-        <f>W10*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X10">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y10">
-        <f>X10 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z10">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA10">
+        <v>1E-4</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
-      <c r="AB10">
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>2E-3</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="7"/>
         <v>1E-4</v>
       </c>
-      <c r="AC10">
+      <c r="AF10">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG10">
         <v>1</v>
       </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>2E-3</v>
-      </c>
-      <c r="AF10">
-        <v>1E-3</v>
-      </c>
-      <c r="AG10">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH10">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ10">
+      <c r="AH10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI10">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:35">
       <c r="B11">
         <v>8</v>
       </c>
@@ -4119,11 +4086,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J11">
+        <f t="shared" si="12"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="13"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="14"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L11" s="4">
@@ -4146,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S11">
         <v>30</v>
@@ -4155,7 +4122,7 @@
         <v>0.8</v>
       </c>
       <c r="U11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V11">
@@ -4165,50 +4132,47 @@
       <c r="W11">
         <v>0.43</v>
       </c>
-      <c r="X11" s="4">
-        <f>W11*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X11">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y11">
-        <f>X11 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z11">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA11">
+        <v>1E-4</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>2E-3</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="7"/>
         <v>1E-4</v>
       </c>
-      <c r="AC11">
+      <c r="AF11">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG11">
         <v>1</v>
       </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>2E-3</v>
-      </c>
-      <c r="AF11">
-        <v>1E-3</v>
-      </c>
-      <c r="AG11">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH11">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ11">
+      <c r="AH11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI11">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:35">
       <c r="B12">
         <v>9</v>
       </c>
@@ -4234,11 +4198,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J12">
-        <f t="shared" ref="J12:J13" si="16">I12*7.5</f>
+        <f t="shared" ref="J12:J13" si="15">I12*7.5</f>
         <v>1.0752025361042621</v>
       </c>
       <c r="K12">
-        <f t="shared" ref="K12:K13" si="17">J12/1000</f>
+        <f t="shared" ref="K12:K13" si="16">J12/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L12" s="4">
@@ -4261,17 +4225,17 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S12">
         <v>30</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T12:T13" si="18">10.6/12*1.07/2</f>
+        <f t="shared" ref="T12:T13" si="17">10.6/12*1.07/2</f>
         <v>0.47258333333333336</v>
       </c>
       <c r="U12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V12">
@@ -4281,50 +4245,47 @@
       <c r="W12">
         <v>0.43</v>
       </c>
-      <c r="X12" s="4">
-        <f>W12*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X12">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y12">
-        <f>X12 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z12">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA12">
+        <v>1E-4</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>2E-3</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="7"/>
         <v>1E-4</v>
       </c>
-      <c r="AC12">
+      <c r="AF12">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG12">
         <v>1</v>
       </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>2E-3</v>
-      </c>
-      <c r="AF12">
-        <v>1E-3</v>
-      </c>
-      <c r="AG12">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH12">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ12">
+      <c r="AH12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI12">
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:35">
       <c r="B13">
         <v>10</v>
       </c>
@@ -4350,11 +4311,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J13">
+        <f t="shared" si="15"/>
+        <v>1.0752025361042621</v>
+      </c>
+      <c r="K13">
         <f t="shared" si="16"/>
-        <v>1.0752025361042621</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="17"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L13" s="4">
@@ -4377,17 +4338,17 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S13">
         <v>30</v>
       </c>
       <c r="T13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.47258333333333336</v>
       </c>
       <c r="U13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V13">
@@ -4397,51 +4358,48 @@
       <c r="W13">
         <v>0.43</v>
       </c>
-      <c r="X13" s="4">
-        <f>W13*1.066</f>
-        <v>0.45838000000000001</v>
+      <c r="X13">
+        <f t="shared" si="6"/>
+        <v>10.32</v>
       </c>
       <c r="Y13">
-        <f>X13 *24</f>
-        <v>11.00112</v>
+        <v>0.06</v>
       </c>
       <c r="Z13">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="AA13">
+        <v>1E-4</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>2E-3</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="7"/>
         <v>1E-4</v>
       </c>
-      <c r="AC13">
+      <c r="AF13">
+        <f t="shared" si="7"/>
+        <v>1E-4</v>
+      </c>
+      <c r="AG13">
         <v>1</v>
       </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>2E-3</v>
-      </c>
-      <c r="AF13">
-        <v>1E-3</v>
-      </c>
-      <c r="AG13">
-        <f t="shared" si="6"/>
-        <v>1E-3</v>
-      </c>
-      <c r="AH13">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ13">
+      <c r="AH13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI13">
         <v>9.375E-2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AJ3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}"/>
+  <autoFilter ref="A3:AI3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4459,7 +4417,7 @@
   <sheetData>
     <row r="1" spans="2:21">
       <c r="B1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="2:21">
@@ -4542,38 +4500,38 @@
     </row>
     <row r="16" spans="2:21">
       <c r="L16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="12:20">
       <c r="L17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" t="s">
         <v>33</v>
       </c>
-      <c r="O17" t="s">
-        <v>37</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>34</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>35</v>
       </c>
-      <c r="R17" t="s">
-        <v>36</v>
-      </c>
       <c r="T17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="12:20">
       <c r="L18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -4594,12 +4552,12 @@
     </row>
     <row r="19" spans="12:20">
       <c r="L19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="12:20">
       <c r="L20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="12:20">
@@ -4608,43 +4566,43 @@
         <v>227</v>
       </c>
       <c r="M21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="12:20">
       <c r="L22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="12:20">
       <c r="L25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N25" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" t="s">
         <v>33</v>
       </c>
-      <c r="O25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>34</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>35</v>
       </c>
-      <c r="R25" t="s">
-        <v>36</v>
-      </c>
       <c r="T25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="12:20">
       <c r="L26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O26">
         <v>2</v>
@@ -4668,53 +4626,53 @@
         <v>60</v>
       </c>
       <c r="M27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="12:20">
       <c r="L28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="12:20">
       <c r="L31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="12:20" ht="18">
       <c r="L32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="10:20">
       <c r="L33" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N33" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" t="s">
         <v>33</v>
       </c>
-      <c r="O33" t="s">
-        <v>37</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>34</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>35</v>
       </c>
-      <c r="R33" t="s">
-        <v>36</v>
-      </c>
       <c r="T33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="10:20">
       <c r="L34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -4737,7 +4695,7 @@
       <c r="J35" s="11"/>
       <c r="K35" s="10"/>
       <c r="L35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="10:20">
@@ -4755,7 +4713,7 @@
     </row>
     <row r="40" spans="10:20">
       <c r="M40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="10:20">
@@ -4763,25 +4721,25 @@
         <v>2.6</v>
       </c>
       <c r="N41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P41">
         <v>2.6</v>
       </c>
       <c r="Q41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="10:20">
       <c r="L42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M42">
         <f>12+1.8+0.5*16+0.2*14</f>
         <v>24.6</v>
       </c>
       <c r="N42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="10:20">
@@ -4792,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="3:14">
@@ -4801,10 +4759,10 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="M51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="3:14">
@@ -4813,7 +4771,7 @@
         <v>2.032520325203252E-10</v>
       </c>
       <c r="M54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="3:14">
@@ -4830,81 +4788,81 @@
     </row>
     <row r="58" spans="3:14">
       <c r="L58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="3:14" ht="18">
       <c r="L59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="3:14">
       <c r="C60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" t="s">
         <v>90</v>
       </c>
-      <c r="D60" t="s">
-        <v>91</v>
-      </c>
       <c r="L60" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M60">
         <f>5*12+7+2*16+14</f>
         <v>113</v>
       </c>
       <c r="N60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="3:14">
       <c r="D61" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61" t="s">
         <v>92</v>
       </c>
-      <c r="E61" t="s">
-        <v>93</v>
-      </c>
       <c r="L61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="3:14">
       <c r="C62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D62">
         <v>7.5</v>
       </c>
       <c r="E62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="3:14">
       <c r="C63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63">
         <v>5.9</v>
       </c>
       <c r="E63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="3:14">
       <c r="C64" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D64" s="13">
         <f>D62-D63</f>
         <v>1.5999999999999996</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F64" s="13"/>
       <c r="K64">
@@ -4912,117 +4870,117 @@
         <v>4.25</v>
       </c>
       <c r="L64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="3:13">
       <c r="C65" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D65" s="13">
         <f>D62+D63</f>
         <v>13.4</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F65" s="13"/>
       <c r="L65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="3:13">
       <c r="C66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D66">
         <f>D62/227.172/1000</f>
         <v>3.3014632084940045E-5</v>
       </c>
       <c r="E66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L66">
         <f>4.25*32</f>
         <v>136</v>
       </c>
       <c r="M66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="3:13">
       <c r="C67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D67">
         <f>D63/227.172/1000</f>
         <v>2.5971510573486172E-5</v>
       </c>
       <c r="E67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L67">
         <f>L66/M60</f>
         <v>1.2035398230088497</v>
       </c>
       <c r="M67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="3:13">
       <c r="C68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D68">
         <f>D66*24.6</f>
         <v>8.1215994928952515E-4</v>
       </c>
       <c r="E68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="3:13">
       <c r="C69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D69">
         <f>D67*24.6</f>
         <v>6.388991601077599E-4</v>
       </c>
       <c r="E69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="3:13">
       <c r="C70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D70">
         <f>D68*1.075/1.05</f>
         <v>8.3149709093927569E-4</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="3:13">
       <c r="C71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D71">
         <f>D69*1.075/1.05</f>
         <v>6.5411104487223025E-4</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="3:13">
       <c r="C75" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="3:13">
@@ -5030,7 +4988,7 @@
         <v>0.33</v>
       </c>
       <c r="E76" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="3:13">
@@ -5038,7 +4996,7 @@
         <v>0.73</v>
       </c>
       <c r="E77" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="3:13">
@@ -5047,7 +5005,7 @@
         <v>3.3000000000000002E-7</v>
       </c>
       <c r="E78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="3:13">
@@ -5056,7 +5014,7 @@
         <v>7.3E-7</v>
       </c>
       <c r="E79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="3:13">
@@ -5065,7 +5023,7 @@
         <v>2.7500000000000001E-8</v>
       </c>
       <c r="E80" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="4:12">
@@ -5074,7 +5032,7 @@
         <v>6.0833333333333329E-8</v>
       </c>
       <c r="E81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="4:12">
@@ -5083,7 +5041,7 @@
         <v>5.5000000000000014E-3</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="4:12">
@@ -5092,7 +5050,7 @@
         <v>1.2166666666666666E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="84" spans="4:12">
@@ -5101,7 +5059,7 @@
         <v>0.13530000000000003</v>
       </c>
       <c r="E84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="4:12">
@@ -5110,7 +5068,7 @@
         <v>0.29930000000000001</v>
       </c>
       <c r="E85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="4:12">
@@ -5119,7 +5077,7 @@
         <v>0.12885714285714289</v>
       </c>
       <c r="E86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="4:12">
@@ -5128,7 +5086,7 @@
         <v>0.28504761904761905</v>
       </c>
       <c r="E87" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="4:12">
@@ -5137,10 +5095,10 @@
         <v>8.4242681454371637E-2</v>
       </c>
       <c r="E89" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="4:12">
@@ -5148,13 +5106,13 @@
         <v>6.905E-6</v>
       </c>
       <c r="E90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K90">
         <v>0.35</v>
       </c>
       <c r="L90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="4:12">
@@ -5163,14 +5121,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K91">
         <f>K90/1000000/24.6</f>
         <v>1.4227642276422762E-8</v>
       </c>
       <c r="L91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92" spans="4:12">
@@ -5179,14 +5137,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K92">
         <f>K91*1.05</f>
         <v>1.4939024390243901E-8</v>
       </c>
       <c r="L92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="4:12">
@@ -5195,7 +5153,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="94" spans="4:12">
@@ -5204,12 +5162,12 @@
         <v>1.4939024390243901E-3</v>
       </c>
       <c r="L94" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="96" spans="4:12">
       <c r="E96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="4:14">
@@ -5217,7 +5175,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="98" spans="4:14">
@@ -5225,13 +5183,13 @@
         <v>9.09</v>
       </c>
       <c r="E98" t="s">
+        <v>120</v>
+      </c>
+      <c r="F98" t="s">
         <v>121</v>
       </c>
-      <c r="F98" t="s">
-        <v>122</v>
-      </c>
       <c r="L98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="4:14">
@@ -5239,20 +5197,20 @@
         <v>7.58</v>
       </c>
       <c r="E99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L99">
         <f>AVERAGE(D127, D86:D87,D70)</f>
         <v>0.10371468607138892</v>
       </c>
       <c r="M99" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N99" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="4:14">
@@ -5260,13 +5218,13 @@
         <v>7.96</v>
       </c>
       <c r="E100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N100" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="101" spans="4:14">
@@ -5274,10 +5232,10 @@
         <v>6.52</v>
       </c>
       <c r="E101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="4:14">
@@ -5285,10 +5243,10 @@
         <v>4.71</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F102" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H102">
         <f>AVERAGE(D102:D105)</f>
@@ -5300,10 +5258,10 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="4:14">
@@ -5311,10 +5269,10 @@
         <v>4.18</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F104" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="4:14">
@@ -5322,10 +5280,10 @@
         <v>4.13</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="106" spans="4:14">
@@ -5333,7 +5291,7 @@
         <v>4.3</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="4:14">
@@ -5341,7 +5299,7 @@
         <v>0.5</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" spans="4:14">
@@ -5349,7 +5307,7 @@
         <v>14.9</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="109" spans="4:14">
@@ -5357,7 +5315,7 @@
         <v>1.9</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="110" spans="4:14">
@@ -5365,7 +5323,7 @@
         <v>12.4</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="111" spans="4:14">
@@ -5373,7 +5331,7 @@
         <v>1.2</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="4:14">
@@ -5381,7 +5339,7 @@
         <v>0.01</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="4:5">
@@ -5389,7 +5347,7 @@
         <v>8.1</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="4:5">
@@ -5397,12 +5355,12 @@
         <v>0.15336312500000002</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="115" spans="4:5">
       <c r="E115" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="4:5">
@@ -5411,7 +5369,7 @@
         <v>8.3333333333333344E-7</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="4:5">
@@ -5420,7 +5378,7 @@
         <v>6.7499999999999993E-4</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118" spans="4:5">
@@ -5429,7 +5387,7 @@
         <v>1.2780260416666668E-5</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" spans="4:5">
@@ -5438,7 +5396,7 @@
         <v>1.9190174630589144E-7</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="120" spans="4:5">
@@ -5447,7 +5405,7 @@
         <v>1.5544041450777204E-4</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="121" spans="4:5">
@@ -5456,7 +5414,7 @@
         <v>2.9430651506428716E-6</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="122" spans="4:5">
@@ -5465,7 +5423,7 @@
         <v>7.8008839961744482E-6</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="123" spans="4:5">
@@ -5474,7 +5432,7 @@
         <v>6.3187160369013026E-3</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="4:5">
@@ -5483,7 +5441,7 @@
         <v>1.1963679474158013E-4</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="4:5">
@@ -5492,7 +5450,7 @@
         <v>7.9866193294166962E-6</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="126" spans="4:5">
@@ -5501,7 +5459,7 @@
         <v>6.4691616568275231E-3</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127" spans="4:5">
@@ -5510,12 +5468,12 @@
         <v>1.224852898544749E-4</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="4:6" ht="198">
       <c r="D130" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="131" spans="4:6">
@@ -5524,10 +5482,10 @@
         <v>1.6000000000000003E-5</v>
       </c>
       <c r="E131" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F131" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="4:6">
@@ -5536,10 +5494,10 @@
         <v>4.5714285714285719E-6</v>
       </c>
       <c r="E132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F132" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="133" spans="4:6">
@@ -5547,10 +5505,10 @@
         <v>630000</v>
       </c>
       <c r="E133" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F133" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="4:6">
@@ -5559,10 +5517,10 @@
         <v>6.3E+17</v>
       </c>
       <c r="E134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F134" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="4:6">
@@ -5571,10 +5529,10 @@
         <v>2880000000000.0005</v>
       </c>
       <c r="E135" t="s">
+        <v>165</v>
+      </c>
+      <c r="F135" t="s">
         <v>166</v>
-      </c>
-      <c r="F135" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="136" spans="4:6">
@@ -5583,10 +5541,10 @@
         <v>227</v>
       </c>
       <c r="E136" t="s">
+        <v>168</v>
+      </c>
+      <c r="F136" t="s">
         <v>169</v>
-      </c>
-      <c r="F136" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="137" spans="4:6">
@@ -5595,10 +5553,10 @@
         <v>653760000000000.13</v>
       </c>
       <c r="E137" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F137" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="138" spans="4:6">
@@ -5607,10 +5565,10 @@
         <v>653760000000.00012</v>
       </c>
       <c r="E138" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F138" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="139" spans="4:6">
@@ -5619,10 +5577,10 @@
         <v>653760000.00000012</v>
       </c>
       <c r="E139" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F139" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23170355-5709-4846-A6D2-985693089006}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4864B005-4B17-454A-A87E-69F9EFFB03A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
@@ -323,7 +323,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
@@ -424,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD5" authorId="4" shapeId="0" xr:uid="{16668028-E470-49D8-A575-5BF14B51E0D7}">
+    <comment ref="AD5" authorId="4" shapeId="0" xr:uid="{763701C8-A8C8-49C4-962B-6929A0DF5A12}">
       <text>
         <r>
           <rPr>
@@ -437,7 +437,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD6" authorId="4" shapeId="0" xr:uid="{2C3E63E2-3AE0-4A5B-8C7D-9BF28330D619}">
+    <comment ref="AD6" authorId="4" shapeId="0" xr:uid="{4D500F6C-2CDA-48D0-80D9-5D4AC31C9C3C}">
       <text>
         <r>
           <rPr>
@@ -551,7 +551,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
@@ -606,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD7" authorId="4" shapeId="0" xr:uid="{52E6596C-BF01-40FE-80EF-E81EF72B1B0A}">
+    <comment ref="AD7" authorId="4" shapeId="0" xr:uid="{29E907F4-9114-40F5-B8A9-1D5E8668BD16}">
       <text>
         <r>
           <rPr>
@@ -619,7 +619,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
@@ -720,7 +720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD8" authorId="4" shapeId="0" xr:uid="{92E5DB6E-68AE-4BE9-AC60-965E4EFEF9C9}">
+    <comment ref="AD8" authorId="4" shapeId="0" xr:uid="{81BDC020-9754-478D-AC3B-9A1496127C48}">
       <text>
         <r>
           <rPr>
@@ -733,7 +733,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
@@ -834,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD9" authorId="4" shapeId="0" xr:uid="{5B2AB557-5C4D-4A18-B601-D1F593004EA2}">
+    <comment ref="AD9" authorId="4" shapeId="0" xr:uid="{76E776A9-FD4C-4460-A07A-3A1EAB0AC004}">
       <text>
         <r>
           <rPr>
@@ -847,11 +847,11 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="17" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
+    <comment ref="J10" authorId="17" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
       <text>
         <r>
           <rPr>
@@ -868,7 +868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V10" authorId="18" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
+    <comment ref="V10" authorId="18" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
       <text>
         <r>
           <rPr>
@@ -931,7 +931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y10" authorId="19" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
+    <comment ref="Y10" authorId="19" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
       <text>
         <r>
           <rPr>
@@ -948,7 +948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD10" authorId="4" shapeId="0" xr:uid="{3A5D2B68-C202-47CB-8961-7FC8DDCB5D87}">
+    <comment ref="AD10" authorId="4" shapeId="0" xr:uid="{F3B35D07-E24B-4A92-98E4-668A2FBD0348}">
       <text>
         <r>
           <rPr>
@@ -961,11 +961,11 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="17" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
+    <comment ref="J11" authorId="17" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
       <text>
         <r>
           <rPr>
@@ -982,7 +982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V11" authorId="18" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
+    <comment ref="V11" authorId="18" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
       <text>
         <r>
           <rPr>
@@ -1045,7 +1045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y11" authorId="19" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
+    <comment ref="Y11" authorId="19" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
       <text>
         <r>
           <rPr>
@@ -1062,7 +1062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD11" authorId="4" shapeId="0" xr:uid="{48DA997C-8DFD-4B73-9E86-327CAC4DFDC5}">
+    <comment ref="AD11" authorId="4" shapeId="0" xr:uid="{CD12DC4D-EC62-491A-943F-527537BC6EEB}">
       <text>
         <r>
           <rPr>
@@ -1075,11 +1075,11 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="17" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
+    <comment ref="J12" authorId="17" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
       <text>
         <r>
           <rPr>
@@ -1096,7 +1096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V12" authorId="18" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
+    <comment ref="V12" authorId="18" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
       <text>
         <r>
           <rPr>
@@ -1159,7 +1159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y12" authorId="19" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
+    <comment ref="Y12" authorId="19" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
       <text>
         <r>
           <rPr>
@@ -1176,7 +1176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD12" authorId="4" shapeId="0" xr:uid="{155DF592-3843-4EA8-9AB8-E5135E1BAF92}">
+    <comment ref="AD12" authorId="4" shapeId="0" xr:uid="{BC16491E-A48A-4531-9C06-C645B35A5967}">
       <text>
         <r>
           <rPr>
@@ -1189,11 +1189,11 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="17" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
+    <comment ref="J13" authorId="17" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
       <text>
         <r>
           <rPr>
@@ -1210,7 +1210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V13" authorId="18" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
+    <comment ref="V13" authorId="18" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
       <text>
         <r>
           <rPr>
@@ -1273,7 +1273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y13" authorId="19" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
+    <comment ref="Y13" authorId="19" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
       <text>
         <r>
           <rPr>
@@ -1290,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD13" authorId="4" shapeId="0" xr:uid="{B66749DF-A4F3-46FC-B53B-BE6D26C8C927}">
+    <comment ref="AD13" authorId="4" shapeId="0" xr:uid="{A817F15E-70E6-400F-B96C-E1316867859F}">
       <text>
         <r>
           <rPr>
@@ -1303,7 +1303,7 @@
           <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day.</t>
+    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
         </r>
       </text>
     </comment>
@@ -3292,7 +3292,7 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I13" si="2">H4/F4*1000</f>
+        <f t="shared" ref="I4:I11" si="2">H4/F4*1000</f>
         <v>0.14336033814723495</v>
       </c>
       <c r="J4">
@@ -3362,8 +3362,8 @@
       <c r="AC4">
         <v>0</v>
       </c>
-      <c r="AD4">
-        <v>2E-3</v>
+      <c r="AD4" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE4">
         <f>0.0001</f>
@@ -3457,7 +3457,7 @@
         <v>0.43</v>
       </c>
       <c r="X5">
-        <f t="shared" ref="X5:X13" si="6">W5 *24</f>
+        <f t="shared" ref="X5:X11" si="6">W5 *24</f>
         <v>10.32</v>
       </c>
       <c r="Y5">
@@ -3475,8 +3475,8 @@
       <c r="AC5">
         <v>0</v>
       </c>
-      <c r="AD5">
-        <v>2E-3</v>
+      <c r="AD5" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE5">
         <f t="shared" ref="AE5:AF13" si="7">0.0001</f>
@@ -3588,8 +3588,8 @@
       <c r="AC6">
         <v>0</v>
       </c>
-      <c r="AD6">
-        <v>2E-3</v>
+      <c r="AD6" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE6">
         <f t="shared" si="7"/>
@@ -3701,8 +3701,8 @@
       <c r="AC7">
         <v>0</v>
       </c>
-      <c r="AD7">
-        <v>2E-3</v>
+      <c r="AD7" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE7">
         <f t="shared" si="7"/>
@@ -3814,8 +3814,8 @@
       <c r="AC8">
         <v>0</v>
       </c>
-      <c r="AD8">
-        <v>2E-3</v>
+      <c r="AD8" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE8">
         <f t="shared" si="7"/>
@@ -3927,8 +3927,8 @@
       <c r="AC9">
         <v>0</v>
       </c>
-      <c r="AD9">
-        <v>2E-3</v>
+      <c r="AD9" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE9">
         <f t="shared" si="7"/>
@@ -3988,8 +3988,8 @@
         <f>L10*J10</f>
         <v>10.752025361042621</v>
       </c>
-      <c r="N10">
-        <v>1E-4</v>
+      <c r="N10" s="21">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -4006,11 +4006,12 @@
       <c r="S10">
         <v>30</v>
       </c>
-      <c r="T10" s="21">
-        <v>1E-3</v>
+      <c r="T10">
+        <f t="shared" ref="T10:T11" si="14">10.6/12*1.07/2</f>
+        <v>0.47258333333333336</v>
       </c>
       <c r="U10">
-        <f t="shared" ref="U10:U13" si="14">4.3 /1000000 *1.07</f>
+        <f t="shared" ref="U10:U13" si="15">4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V10">
@@ -4039,8 +4040,8 @@
       <c r="AC10">
         <v>0</v>
       </c>
-      <c r="AD10">
-        <v>2E-3</v>
+      <c r="AD10" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE10">
         <f t="shared" si="7"/>
@@ -4100,8 +4101,8 @@
         <f>L11*J11</f>
         <v>10.752025361042621</v>
       </c>
-      <c r="N11">
-        <v>1E-4</v>
+      <c r="N11" s="21">
+        <v>0.01</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -4118,11 +4119,12 @@
       <c r="S11">
         <v>30</v>
       </c>
-      <c r="T11" s="21">
-        <v>0.8</v>
+      <c r="T11">
+        <f t="shared" si="14"/>
+        <v>0.47258333333333336</v>
       </c>
       <c r="U11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V11">
@@ -4151,8 +4153,8 @@
       <c r="AC11">
         <v>0</v>
       </c>
-      <c r="AD11">
-        <v>2E-3</v>
+      <c r="AD11" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE11">
         <f t="shared" si="7"/>
@@ -4194,15 +4196,15 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
+        <f>H12/F12*1000</f>
         <v>0.14336033814723495</v>
       </c>
       <c r="J12">
-        <f t="shared" ref="J12:J13" si="15">I12*7.5</f>
+        <f t="shared" ref="J12:J13" si="16">I12*7.5</f>
         <v>1.0752025361042621</v>
       </c>
       <c r="K12">
-        <f t="shared" ref="K12:K13" si="16">J12/1000</f>
+        <f t="shared" ref="K12:K13" si="17">J12/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L12" s="4">
@@ -4212,8 +4214,8 @@
         <f>L12*J12</f>
         <v>10.752025361042621</v>
       </c>
-      <c r="N12" s="21">
-        <v>9.9999999999999995E-7</v>
+      <c r="N12">
+        <v>1E-4</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -4230,12 +4232,11 @@
       <c r="S12">
         <v>30</v>
       </c>
-      <c r="T12">
-        <f t="shared" ref="T12:T13" si="17">10.6/12*1.07/2</f>
-        <v>0.47258333333333336</v>
+      <c r="T12" s="21">
+        <v>1E-3</v>
       </c>
       <c r="U12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V12">
@@ -4246,7 +4247,7 @@
         <v>0.43</v>
       </c>
       <c r="X12">
-        <f t="shared" si="6"/>
+        <f>W12 *24</f>
         <v>10.32</v>
       </c>
       <c r="Y12">
@@ -4264,8 +4265,8 @@
       <c r="AC12">
         <v>0</v>
       </c>
-      <c r="AD12">
-        <v>2E-3</v>
+      <c r="AD12" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE12">
         <f t="shared" si="7"/>
@@ -4307,15 +4308,15 @@
         <v>0.20349999999999999</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f>H13/F13*1000</f>
         <v>0.14336033814723495</v>
       </c>
       <c r="J13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L13" s="4">
@@ -4325,8 +4326,8 @@
         <f>L13*J13</f>
         <v>10.752025361042621</v>
       </c>
-      <c r="N13" s="21">
-        <v>0.01</v>
+      <c r="N13">
+        <v>1E-4</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -4343,12 +4344,11 @@
       <c r="S13">
         <v>30</v>
       </c>
-      <c r="T13">
-        <f t="shared" si="17"/>
-        <v>0.47258333333333336</v>
+      <c r="T13" s="21">
+        <v>0.8</v>
       </c>
       <c r="U13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V13">
@@ -4359,7 +4359,7 @@
         <v>0.43</v>
       </c>
       <c r="X13">
-        <f t="shared" si="6"/>
+        <f>W13 *24</f>
         <v>10.32</v>
       </c>
       <c r="Y13">
@@ -4377,8 +4377,8 @@
       <c r="AC13">
         <v>0</v>
       </c>
-      <c r="AD13">
-        <v>2E-3</v>
+      <c r="AD13" s="4">
+        <v>0.02</v>
       </c>
       <c r="AE13">
         <f t="shared" si="7"/>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4864B005-4B17-454A-A87E-69F9EFFB03A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3071D129-70BF-4C3B-B83E-C081A60BD1B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
@@ -38,19 +38,14 @@
     <author>tc={D83D8722-287D-8543-91DC-DFD968583D4B}</author>
     <author>tc={4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}</author>
     <author>tc={8B1BECD1-664B-894E-902F-58308D659DA9}</author>
-    <author>tc={944B0A6E-7F35-8040-8354-541096ED2DBE}</author>
     <author>tc={0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}</author>
     <author>tc={3C0608B8-171F-064A-822A-A3CC6DDC9FC4}</author>
-    <author>tc={4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}</author>
     <author>tc={8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}</author>
     <author>tc={D578DC42-15AA-9242-8F7A-DCCCBD7DB327}</author>
-    <author>tc={D9858DC7-D04C-4A4F-872C-0C59D675639A}</author>
     <author>tc={28910C3F-267C-EF48-8C2C-F6C895522D82}</author>
     <author>tc={E7A076DC-8E76-1148-951F-1F3AE0C081A3}</author>
-    <author>tc={8ABD701E-78D0-4A47-8F33-59280C42BAAB}</author>
     <author>tc={E68EDC32-0C11-F24F-BC92-6599E44DEE2B}</author>
     <author>tc={03DDDF21-1FDE-1A44-92CB-02C9D1E67681}</author>
-    <author>tc={74D124C3-18A4-4549-83DD-7E733D9BD57D}</author>
   </authors>
   <commentList>
     <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{C7B782E2-F656-DB45-97AC-D2B1A4310A43}">
@@ -257,56 +252,9 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Foulquier 2010 Relating</t>
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
@@ -320,10 +268,10 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
@@ -407,24 +355,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y5" authorId="7" shapeId="0" xr:uid="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
+    <comment ref="Y5" authorId="3" shapeId="0" xr:uid="{E0003C2A-83D2-486E-9F95-6F942D601306}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD5" authorId="4" shapeId="0" xr:uid="{763701C8-A8C8-49C4-962B-6929A0DF5A12}">
+    <comment ref="AD5" authorId="4" shapeId="0" xr:uid="{7FFF54EE-822F-4E24-82E6-9B08E6ADA601}">
       <text>
         <r>
           <rPr>
@@ -434,14 +381,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="8" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
+    <comment ref="J6" authorId="7" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
       <text>
         <r>
           <rPr>
@@ -458,7 +405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="9" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
+    <comment ref="V6" authorId="8" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
       <text>
         <r>
           <rPr>
@@ -521,24 +468,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y6" authorId="10" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
+    <comment ref="Y6" authorId="3" shapeId="0" xr:uid="{C1E8E5BB-5C92-464C-B317-D647AD291D97}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD6" authorId="4" shapeId="0" xr:uid="{4D500F6C-2CDA-48D0-80D9-5D4AC31C9C3C}">
+    <comment ref="AD6" authorId="4" shapeId="0" xr:uid="{D78B7DB3-DB64-47EA-963E-B943EEB5ED7C}">
       <text>
         <r>
           <rPr>
@@ -548,14 +494,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="11" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
+    <comment ref="J7" authorId="9" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
       <text>
         <r>
           <rPr>
@@ -572,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V7" authorId="12" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
+    <comment ref="V7" authorId="10" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
       <text>
         <r>
           <rPr>
@@ -589,24 +535,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y7" authorId="13" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
+    <comment ref="Y7" authorId="3" shapeId="0" xr:uid="{21FB828A-8F4B-49F5-BC35-7162AF9D019F}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD7" authorId="4" shapeId="0" xr:uid="{29E907F4-9114-40F5-B8A9-1D5E8668BD16}">
+    <comment ref="AD7" authorId="4" shapeId="0" xr:uid="{DF58DDD3-DEE2-46D2-801E-38066E3FE332}">
       <text>
         <r>
           <rPr>
@@ -616,14 +561,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="14" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
+    <comment ref="J8" authorId="11" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
       <text>
         <r>
           <rPr>
@@ -640,7 +585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V8" authorId="15" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
+    <comment ref="V8" authorId="12" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
       <text>
         <r>
           <rPr>
@@ -703,24 +648,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y8" authorId="16" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
+    <comment ref="Y8" authorId="3" shapeId="0" xr:uid="{4A3BB5D2-A2F4-404E-9981-B4AC114D67D5}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD8" authorId="4" shapeId="0" xr:uid="{81BDC020-9754-478D-AC3B-9A1496127C48}">
+    <comment ref="AD8" authorId="4" shapeId="0" xr:uid="{09CEFCD2-C7F3-4A3E-8EAD-6783F81DB573}">
       <text>
         <r>
           <rPr>
@@ -730,14 +674,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="17" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
+    <comment ref="J9" authorId="13" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
       <text>
         <r>
           <rPr>
@@ -754,7 +698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V9" authorId="18" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
+    <comment ref="V9" authorId="14" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
       <text>
         <r>
           <rPr>
@@ -817,24 +761,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y9" authorId="19" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
+    <comment ref="Y9" authorId="3" shapeId="0" xr:uid="{61C481F3-24C5-44D2-A4EE-6F00A096C944}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD9" authorId="4" shapeId="0" xr:uid="{76E776A9-FD4C-4460-A07A-3A1EAB0AC004}">
+    <comment ref="AD9" authorId="4" shapeId="0" xr:uid="{A1052B11-CDA7-4355-85C8-B36DCDCBFA84}">
       <text>
         <r>
           <rPr>
@@ -844,14 +787,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="17" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
+    <comment ref="J10" authorId="13" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
       <text>
         <r>
           <rPr>
@@ -868,7 +811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V10" authorId="18" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
+    <comment ref="V10" authorId="14" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
       <text>
         <r>
           <rPr>
@@ -931,24 +874,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y10" authorId="19" shapeId="0" xr:uid="{5F6BAB42-F9A7-4880-A8DF-F9E5F4DEAA58}">
+    <comment ref="Y10" authorId="3" shapeId="0" xr:uid="{EBFD2544-76F8-46EB-966B-813ED3C87C82}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD10" authorId="4" shapeId="0" xr:uid="{F3B35D07-E24B-4A92-98E4-668A2FBD0348}">
+    <comment ref="AD10" authorId="4" shapeId="0" xr:uid="{531A283A-AC70-4152-9BE6-43C54300A95C}">
       <text>
         <r>
           <rPr>
@@ -958,14 +900,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="17" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
+    <comment ref="J11" authorId="13" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
       <text>
         <r>
           <rPr>
@@ -982,7 +924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V11" authorId="18" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
+    <comment ref="V11" authorId="14" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
       <text>
         <r>
           <rPr>
@@ -1045,24 +987,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y11" authorId="19" shapeId="0" xr:uid="{131DF270-3C73-49B5-BD68-1F49168AEBBC}">
+    <comment ref="Y11" authorId="3" shapeId="0" xr:uid="{CA845B26-4E91-41C7-9B80-A14104B366DD}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD11" authorId="4" shapeId="0" xr:uid="{CD12DC4D-EC62-491A-943F-527537BC6EEB}">
+    <comment ref="AD11" authorId="4" shapeId="0" xr:uid="{27CA7D1E-600E-4B66-8951-581265F0DEE5}">
       <text>
         <r>
           <rPr>
@@ -1072,14 +1013,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="17" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
+    <comment ref="J12" authorId="13" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
       <text>
         <r>
           <rPr>
@@ -1096,7 +1037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V12" authorId="18" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
+    <comment ref="V12" authorId="14" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
       <text>
         <r>
           <rPr>
@@ -1159,24 +1100,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y12" authorId="19" shapeId="0" xr:uid="{5E9B9DF4-3124-4011-8650-F6C413EFC23B}">
+    <comment ref="Y12" authorId="3" shapeId="0" xr:uid="{9119942B-138C-4E9B-896C-8017896C61D4}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD12" authorId="4" shapeId="0" xr:uid="{BC16491E-A48A-4531-9C06-C645B35A5967}">
+    <comment ref="AD12" authorId="4" shapeId="0" xr:uid="{1EDBEFA8-BB0A-4540-8BFB-23D5EA138441}">
       <text>
         <r>
           <rPr>
@@ -1186,14 +1126,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="17" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
+    <comment ref="J13" authorId="13" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
       <text>
         <r>
           <rPr>
@@ -1210,7 +1150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V13" authorId="18" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
+    <comment ref="V13" authorId="14" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
       <text>
         <r>
           <rPr>
@@ -1273,24 +1213,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y13" authorId="19" shapeId="0" xr:uid="{DD778B4E-FBBE-482A-A38D-F6A2FD45AD3D}">
+    <comment ref="Y13" authorId="3" shapeId="0" xr:uid="{9D71E412-A9DC-488B-91B8-61FE9E77AC39}">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Foulquier 2010 Relating</t>
+    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
         </r>
       </text>
     </comment>
-    <comment ref="AD13" authorId="4" shapeId="0" xr:uid="{A817F15E-70E6-400F-B96C-E1316867859F}">
+    <comment ref="AD13" authorId="4" shapeId="0" xr:uid="{AC533041-3EAD-4291-8203-F990E3DAA62A}">
       <text>
         <r>
           <rPr>
@@ -1300,10 +1239,10 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>[Threaded comment]
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Equating organic carbon to biofilm, and bacterial uptake to growth, we used the uptake rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times this observed growth rate which might have been derived under maybe non -ideal conditions</t>
+    Foulquier et al. (2010): of 0.35 / day </t>
         </r>
       </text>
     </comment>
@@ -1988,9 +1927,6 @@
     <t>g COD / g biomass</t>
   </si>
   <si>
-    <t>now same as microbes. Alternatively , 0.1 as in Lindeman, but thats less. Lezts stick  the original plan. Thats dry mass alreeady. Alhtough, no, the original plan was acetate - that does not hold for fauna. It barely holds for MO. 0.1</t>
-  </si>
-  <si>
     <t>mortalityFraction_per_degree</t>
   </si>
   <si>
@@ -2400,13 +2336,18 @@
   <si>
     <t>rate constant per hour for bacterial uptake and oxidation of acetate Gerritse et al. (1992), assuming COD can be degraded like acetate, which is an error-prone assumption</t>
   </si>
+  <si>
+    <t>Alternatively , 0.1 as in Lindeman. Thats dry mass already.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000000000E+00"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -2583,7 +2524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2617,6 +2558,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3067,7 +3010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}">
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -3075,6 +3018,7 @@
     <col min="11" max="11" width="11.19921875" customWidth="1"/>
     <col min="13" max="13" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.3984375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3089,22 +3033,22 @@
         <v>47</v>
       </c>
       <c r="F1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" t="s">
         <v>178</v>
       </c>
-      <c r="G1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>179</v>
-      </c>
-      <c r="L1" t="s">
-        <v>180</v>
       </c>
       <c r="M1" t="s">
         <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O1" t="s">
         <v>5</v>
@@ -3113,31 +3057,31 @@
         <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y1" t="s">
         <v>187</v>
       </c>
-      <c r="Y1" t="s">
-        <v>87</v>
-      </c>
       <c r="Z1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AG1" t="s">
         <v>182</v>
       </c>
-      <c r="AA1" t="s">
-        <v>177</v>
-      </c>
-      <c r="AD1" t="s">
+      <c r="AI1" t="s">
         <v>185</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:35">
@@ -3174,7 +3118,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>46</v>
@@ -3183,7 +3127,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -3267,7 +3211,7 @@
         <v>52</v>
       </c>
       <c r="AI3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -3362,8 +3306,8 @@
       <c r="AC4">
         <v>0</v>
       </c>
-      <c r="AD4" s="4">
-        <v>0.02</v>
+      <c r="AD4" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE4">
         <f>0.0001</f>
@@ -3475,8 +3419,8 @@
       <c r="AC5">
         <v>0</v>
       </c>
-      <c r="AD5" s="4">
-        <v>0.02</v>
+      <c r="AD5" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE5">
         <f t="shared" ref="AE5:AF13" si="7">0.0001</f>
@@ -3588,8 +3532,8 @@
       <c r="AC6">
         <v>0</v>
       </c>
-      <c r="AD6" s="4">
-        <v>0.02</v>
+      <c r="AD6" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE6">
         <f t="shared" si="7"/>
@@ -3701,8 +3645,8 @@
       <c r="AC7">
         <v>0</v>
       </c>
-      <c r="AD7" s="4">
-        <v>0.02</v>
+      <c r="AD7" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE7">
         <f t="shared" si="7"/>
@@ -3814,8 +3758,8 @@
       <c r="AC8">
         <v>0</v>
       </c>
-      <c r="AD8" s="4">
-        <v>0.02</v>
+      <c r="AD8" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE8">
         <f t="shared" si="7"/>
@@ -3927,8 +3871,8 @@
       <c r="AC9">
         <v>0</v>
       </c>
-      <c r="AD9" s="4">
-        <v>0.02</v>
+      <c r="AD9" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE9">
         <f t="shared" si="7"/>
@@ -4040,8 +3984,8 @@
       <c r="AC10">
         <v>0</v>
       </c>
-      <c r="AD10" s="4">
-        <v>0.02</v>
+      <c r="AD10" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE10">
         <f t="shared" si="7"/>
@@ -4153,8 +4097,8 @@
       <c r="AC11">
         <v>0</v>
       </c>
-      <c r="AD11" s="4">
-        <v>0.02</v>
+      <c r="AD11" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE11">
         <f t="shared" si="7"/>
@@ -4265,8 +4209,8 @@
       <c r="AC12">
         <v>0</v>
       </c>
-      <c r="AD12" s="4">
-        <v>0.02</v>
+      <c r="AD12" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE12">
         <f t="shared" si="7"/>
@@ -4377,8 +4321,8 @@
       <c r="AC13">
         <v>0</v>
       </c>
-      <c r="AD13" s="4">
-        <v>0.02</v>
+      <c r="AD13" s="23">
+        <v>0.35</v>
       </c>
       <c r="AE13">
         <f t="shared" si="7"/>
@@ -4397,6 +4341,12 @@
       <c r="AI13">
         <v>9.375E-2</v>
       </c>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="AD14" s="23"/>
+    </row>
+    <row r="15" spans="1:35">
+      <c r="AD15" s="24"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AI3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}"/>
@@ -4636,7 +4586,7 @@
     </row>
     <row r="31" spans="12:20">
       <c r="L31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="12:20" ht="18">
@@ -4739,7 +4689,7 @@
         <v>24.6</v>
       </c>
       <c r="N42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="10:20">
@@ -4771,7 +4721,7 @@
         <v>2.032520325203252E-10</v>
       </c>
       <c r="M54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="3:14">
@@ -4798,10 +4748,10 @@
     </row>
     <row r="60" spans="3:14">
       <c r="C60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" t="s">
         <v>89</v>
-      </c>
-      <c r="D60" t="s">
-        <v>90</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>84</v>
@@ -4816,10 +4766,10 @@
     </row>
     <row r="61" spans="3:14">
       <c r="D61" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" t="s">
         <v>91</v>
-      </c>
-      <c r="E61" t="s">
-        <v>92</v>
       </c>
       <c r="L61" t="s">
         <v>79</v>
@@ -4827,13 +4777,13 @@
     </row>
     <row r="62" spans="3:14">
       <c r="C62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62">
         <v>7.5</v>
       </c>
       <c r="E62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L62" t="s">
         <v>80</v>
@@ -4841,13 +4791,13 @@
     </row>
     <row r="63" spans="3:14">
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63">
         <v>5.9</v>
       </c>
       <c r="E63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L63" t="s">
         <v>81</v>
@@ -4855,14 +4805,14 @@
     </row>
     <row r="64" spans="3:14">
       <c r="C64" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D64" s="13">
         <f>D62-D63</f>
         <v>1.5999999999999996</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F64" s="13"/>
       <c r="K64">
@@ -4875,14 +4825,14 @@
     </row>
     <row r="65" spans="3:13">
       <c r="C65" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D65" s="13">
         <f>D62+D63</f>
         <v>13.4</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F65" s="13"/>
       <c r="L65" t="s">
@@ -4891,14 +4841,14 @@
     </row>
     <row r="66" spans="3:13">
       <c r="C66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D66">
         <f>D62/227.172/1000</f>
         <v>3.3014632084940045E-5</v>
       </c>
       <c r="E66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L66">
         <f>4.25*32</f>
@@ -4910,14 +4860,14 @@
     </row>
     <row r="67" spans="3:13">
       <c r="C67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D67">
         <f>D63/227.172/1000</f>
         <v>2.5971510573486172E-5</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L67">
         <f>L66/M60</f>
@@ -4929,58 +4879,58 @@
     </row>
     <row r="68" spans="3:13">
       <c r="C68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D68">
         <f>D66*24.6</f>
         <v>8.1215994928952515E-4</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="3:13">
       <c r="C69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D69">
         <f>D67*24.6</f>
         <v>6.388991601077599E-4</v>
       </c>
       <c r="E69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="3:13">
       <c r="C70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D70">
         <f>D68*1.075/1.05</f>
         <v>8.3149709093927569E-4</v>
       </c>
       <c r="E70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="3:13">
       <c r="C71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D71">
         <f>D69*1.075/1.05</f>
         <v>6.5411104487223025E-4</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="3:13">
       <c r="C75" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="3:13">
@@ -4988,7 +4938,7 @@
         <v>0.33</v>
       </c>
       <c r="E76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="3:13">
@@ -4996,7 +4946,7 @@
         <v>0.73</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="3:13">
@@ -5005,7 +4955,7 @@
         <v>3.3000000000000002E-7</v>
       </c>
       <c r="E78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="3:13">
@@ -5014,7 +4964,7 @@
         <v>7.3E-7</v>
       </c>
       <c r="E79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="3:13">
@@ -5023,7 +4973,7 @@
         <v>2.7500000000000001E-8</v>
       </c>
       <c r="E80" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="4:12">
@@ -5032,7 +4982,7 @@
         <v>6.0833333333333329E-8</v>
       </c>
       <c r="E81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="4:12">
@@ -5041,7 +4991,7 @@
         <v>5.5000000000000014E-3</v>
       </c>
       <c r="E82" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="4:12">
@@ -5050,7 +5000,7 @@
         <v>1.2166666666666666E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="4:12">
@@ -5059,7 +5009,7 @@
         <v>0.13530000000000003</v>
       </c>
       <c r="E84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="4:12">
@@ -5068,7 +5018,7 @@
         <v>0.29930000000000001</v>
       </c>
       <c r="E85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="4:12">
@@ -5077,7 +5027,7 @@
         <v>0.12885714285714289</v>
       </c>
       <c r="E86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="4:12">
@@ -5086,7 +5036,7 @@
         <v>0.28504761904761905</v>
       </c>
       <c r="E87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="4:12">
@@ -5095,10 +5045,10 @@
         <v>8.4242681454371637E-2</v>
       </c>
       <c r="E89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" spans="4:12">
@@ -5106,13 +5056,13 @@
         <v>6.905E-6</v>
       </c>
       <c r="E90" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K90">
         <v>0.35</v>
       </c>
       <c r="L90" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="91" spans="4:12">
@@ -5121,14 +5071,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K91">
         <f>K90/1000000/24.6</f>
         <v>1.4227642276422762E-8</v>
       </c>
       <c r="L91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="4:12">
@@ -5137,14 +5087,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E92" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K92">
         <f>K91*1.05</f>
         <v>1.4939024390243901E-8</v>
       </c>
       <c r="L92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93" spans="4:12">
@@ -5153,7 +5103,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="4:12">
@@ -5162,12 +5112,12 @@
         <v>1.4939024390243901E-3</v>
       </c>
       <c r="L94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="96" spans="4:12">
       <c r="E96" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="4:14">
@@ -5175,7 +5125,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="4:14">
@@ -5183,13 +5133,13 @@
         <v>9.09</v>
       </c>
       <c r="E98" t="s">
+        <v>119</v>
+      </c>
+      <c r="F98" t="s">
         <v>120</v>
       </c>
-      <c r="F98" t="s">
-        <v>121</v>
-      </c>
       <c r="L98" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="99" spans="4:14">
@@ -5197,20 +5147,20 @@
         <v>7.58</v>
       </c>
       <c r="E99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F99" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L99">
         <f>AVERAGE(D127, D86:D87,D70)</f>
         <v>0.10371468607138892</v>
       </c>
       <c r="M99" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N99" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="4:14">
@@ -5218,13 +5168,13 @@
         <v>7.96</v>
       </c>
       <c r="E100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N100" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="4:14">
@@ -5232,10 +5182,10 @@
         <v>6.52</v>
       </c>
       <c r="E101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="4:14">
@@ -5243,10 +5193,10 @@
         <v>4.71</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F102" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H102">
         <f>AVERAGE(D102:D105)</f>
@@ -5258,10 +5208,10 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="4:14">
@@ -5269,10 +5219,10 @@
         <v>4.18</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F104" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="4:14">
@@ -5280,10 +5230,10 @@
         <v>4.13</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F105" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="106" spans="4:14">
@@ -5291,7 +5241,7 @@
         <v>4.3</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="4:14">
@@ -5299,7 +5249,7 @@
         <v>0.5</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="108" spans="4:14">
@@ -5307,7 +5257,7 @@
         <v>14.9</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="4:14">
@@ -5315,7 +5265,7 @@
         <v>1.9</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="110" spans="4:14">
@@ -5323,7 +5273,7 @@
         <v>12.4</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111" spans="4:14">
@@ -5331,7 +5281,7 @@
         <v>1.2</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112" spans="4:14">
@@ -5339,7 +5289,7 @@
         <v>0.01</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="4:5">
@@ -5347,7 +5297,7 @@
         <v>8.1</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114" spans="4:5">
@@ -5355,12 +5305,12 @@
         <v>0.15336312500000002</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="4:5">
       <c r="E115" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="116" spans="4:5">
@@ -5369,7 +5319,7 @@
         <v>8.3333333333333344E-7</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="4:5">
@@ -5378,7 +5328,7 @@
         <v>6.7499999999999993E-4</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="118" spans="4:5">
@@ -5387,7 +5337,7 @@
         <v>1.2780260416666668E-5</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="119" spans="4:5">
@@ -5396,7 +5346,7 @@
         <v>1.9190174630589144E-7</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="120" spans="4:5">
@@ -5405,7 +5355,7 @@
         <v>1.5544041450777204E-4</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="121" spans="4:5">
@@ -5414,7 +5364,7 @@
         <v>2.9430651506428716E-6</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122" spans="4:5">
@@ -5423,7 +5373,7 @@
         <v>7.8008839961744482E-6</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="123" spans="4:5">
@@ -5432,7 +5382,7 @@
         <v>6.3187160369013026E-3</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="124" spans="4:5">
@@ -5441,7 +5391,7 @@
         <v>1.1963679474158013E-4</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125" spans="4:5">
@@ -5450,7 +5400,7 @@
         <v>7.9866193294166962E-6</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126" spans="4:5">
@@ -5459,7 +5409,7 @@
         <v>6.4691616568275231E-3</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="127" spans="4:5">
@@ -5468,12 +5418,12 @@
         <v>1.224852898544749E-4</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="130" spans="4:6" ht="198">
       <c r="D130" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="4:6">
@@ -5482,10 +5432,10 @@
         <v>1.6000000000000003E-5</v>
       </c>
       <c r="E131" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="4:6">
@@ -5494,10 +5444,10 @@
         <v>4.5714285714285719E-6</v>
       </c>
       <c r="E132" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F132" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="133" spans="4:6">
@@ -5505,10 +5455,10 @@
         <v>630000</v>
       </c>
       <c r="E133" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="4:6">
@@ -5517,10 +5467,10 @@
         <v>6.3E+17</v>
       </c>
       <c r="E134" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F134" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135" spans="4:6">
@@ -5529,10 +5479,10 @@
         <v>2880000000000.0005</v>
       </c>
       <c r="E135" t="s">
+        <v>164</v>
+      </c>
+      <c r="F135" t="s">
         <v>165</v>
-      </c>
-      <c r="F135" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="136" spans="4:6">
@@ -5541,10 +5491,10 @@
         <v>227</v>
       </c>
       <c r="E136" t="s">
+        <v>167</v>
+      </c>
+      <c r="F136" t="s">
         <v>168</v>
-      </c>
-      <c r="F136" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="137" spans="4:6">
@@ -5553,10 +5503,10 @@
         <v>653760000000000.13</v>
       </c>
       <c r="E137" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F137" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="4:6">
@@ -5565,10 +5515,10 @@
         <v>653760000000.00012</v>
       </c>
       <c r="E138" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F138" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="4:6">
@@ -5577,10 +5527,10 @@
         <v>653760000.00000012</v>
       </c>
       <c r="E139" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F139" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\freefilesyncHBU\projects\git\gw_ecosystem_services\Fulda_plains\R_git\gtm_River_Fulda_floodplain\gtm_River_Fulda_floodplain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susanneschmidt/Documents/head/Arbeit/projects/git/gw_ecosystem_services/Fulda_plains/R_git/gtm_River_Fulda_floodplain/gtm_River_Fulda_floodplain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3071D129-70BF-4C3B-B83E-C081A60BD1B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114C3D93-D6F4-3543-8C47-954D1BBB2C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="23040" windowHeight="7140" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="24360" windowHeight="13200" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -38,14 +49,40 @@
     <author>tc={D83D8722-287D-8543-91DC-DFD968583D4B}</author>
     <author>tc={4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}</author>
     <author>tc={8B1BECD1-664B-894E-902F-58308D659DA9}</author>
+    <author>tc={B2EEDDFE-EFB6-B842-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-8544-91DC-DFD968583D4B}</author>
     <author>tc={0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}</author>
     <author>tc={3C0608B8-171F-064A-822A-A3CC6DDC9FC4}</author>
+    <author>tc={B2EEDDFE-EFB6-B843-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-8545-91DC-DFD968583D4B}</author>
     <author>tc={8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}</author>
     <author>tc={D578DC42-15AA-9242-8F7A-DCCCBD7DB327}</author>
+    <author>tc={B2EEDDFE-EFB6-B844-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-8546-91DC-DFD968583D4B}</author>
     <author>tc={28910C3F-267C-EF48-8C2C-F6C895522D82}</author>
     <author>tc={E7A076DC-8E76-1148-951F-1F3AE0C081A3}</author>
+    <author>tc={B2EEDDFE-EFB6-B845-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-8547-91DC-DFD968583D4B}</author>
     <author>tc={E68EDC32-0C11-F24F-BC92-6599E44DEE2B}</author>
     <author>tc={03DDDF21-1FDE-1A44-92CB-02C9D1E67681}</author>
+    <author>tc={B2EEDDFE-EFB6-B846-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-8548-91DC-DFD968583D4B}</author>
+    <author>tc={E68EDC32-0C11-F250-BC92-6599E44DEE2B}</author>
+    <author>tc={03DDDF21-1FDE-1A45-92CB-02C9D1E67681}</author>
+    <author>tc={B2EEDDFE-EFB6-B847-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-8549-91DC-DFD968583D4B}</author>
+    <author>tc={E68EDC32-0C11-F251-BC92-6599E44DEE2B}</author>
+    <author>tc={03DDDF21-1FDE-1A46-92CB-02C9D1E67681}</author>
+    <author>tc={B2EEDDFE-EFB6-B848-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-854A-91DC-DFD968583D4B}</author>
+    <author>tc={E68EDC32-0C11-F252-BC92-6599E44DEE2B}</author>
+    <author>tc={03DDDF21-1FDE-1A47-92CB-02C9D1E67681}</author>
+    <author>tc={B2EEDDFE-EFB6-B849-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-854B-91DC-DFD968583D4B}</author>
+    <author>tc={E68EDC32-0C11-F253-BC92-6599E44DEE2B}</author>
+    <author>tc={03DDDF21-1FDE-1A48-92CB-02C9D1E67681}</author>
+    <author>tc={B2EEDDFE-EFB6-B84A-B3B1-49218DCB8340}</author>
+    <author>tc={D83D8722-287D-854C-91DC-DFD968583D4B}</author>
   </authors>
   <commentList>
     <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{C7B782E2-F656-DB45-97AC-D2B1A4310A43}">
@@ -118,1132 +155,342 @@
     </comment>
     <comment ref="J4" authorId="1" shapeId="0" xr:uid="{BC23984A-4BE5-DB42-8CB2-421621628373}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
     <comment ref="V4" authorId="2" shapeId="0" xr:uid="{A973AB73-A4B2-DB42-8CE2-2E9D2BA6D327}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="Y4" authorId="3" shapeId="0" xr:uid="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="4" shapeId="0" xr:uid="{D83D8722-287D-8543-91DC-DFD968583D4B}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
     <comment ref="J5" authorId="5" shapeId="0" xr:uid="{4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
     <comment ref="V5" authorId="6" shapeId="0" xr:uid="{8B1BECD1-664B-894E-902F-58308D659DA9}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y5" authorId="3" shapeId="0" xr:uid="{E0003C2A-83D2-486E-9F95-6F942D601306}">
+    <comment ref="Y5" authorId="7" shapeId="0" xr:uid="{E0003C2A-83D2-486E-9F95-6F942D601306}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD5" authorId="4" shapeId="0" xr:uid="{7FFF54EE-822F-4E24-82E6-9B08E6ADA601}">
+    <comment ref="AD5" authorId="8" shapeId="0" xr:uid="{C4A4A8D0-AF69-4FCB-8304-3233EB12794A}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J6" authorId="7" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
+    <comment ref="J6" authorId="9" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="8" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
+    <comment ref="V6" authorId="10" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y6" authorId="3" shapeId="0" xr:uid="{C1E8E5BB-5C92-464C-B317-D647AD291D97}">
+    <comment ref="Y6" authorId="11" shapeId="0" xr:uid="{C1E8E5BB-5C92-464C-B317-D647AD291D97}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD6" authorId="4" shapeId="0" xr:uid="{D78B7DB3-DB64-47EA-963E-B943EEB5ED7C}">
+    <comment ref="AD6" authorId="12" shapeId="0" xr:uid="{B67B6ED2-69EE-45C0-AC7F-50528141EB4C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J7" authorId="9" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
+    <comment ref="J7" authorId="13" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V7" authorId="10" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
+    <comment ref="V7" authorId="14" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
       </text>
     </comment>
-    <comment ref="Y7" authorId="3" shapeId="0" xr:uid="{21FB828A-8F4B-49F5-BC35-7162AF9D019F}">
+    <comment ref="Y7" authorId="15" shapeId="0" xr:uid="{21FB828A-8F4B-49F5-BC35-7162AF9D019F}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD7" authorId="4" shapeId="0" xr:uid="{DF58DDD3-DEE2-46D2-801E-38066E3FE332}">
+    <comment ref="AD7" authorId="16" shapeId="0" xr:uid="{4BC3115E-C00E-4DF5-8F6D-C7F2D22759E4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J8" authorId="11" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
+    <comment ref="J8" authorId="17" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V8" authorId="12" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
+    <comment ref="V8" authorId="18" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y8" authorId="3" shapeId="0" xr:uid="{4A3BB5D2-A2F4-404E-9981-B4AC114D67D5}">
+    <comment ref="Y8" authorId="19" shapeId="0" xr:uid="{4A3BB5D2-A2F4-404E-9981-B4AC114D67D5}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD8" authorId="4" shapeId="0" xr:uid="{09CEFCD2-C7F3-4A3E-8EAD-6783F81DB573}">
+    <comment ref="AD8" authorId="20" shapeId="0" xr:uid="{B2E603BB-5962-4CD4-BBF0-09C509CEC7F9}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J9" authorId="13" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
+    <comment ref="J9" authorId="21" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V9" authorId="14" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
+    <comment ref="V9" authorId="22" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y9" authorId="3" shapeId="0" xr:uid="{61C481F3-24C5-44D2-A4EE-6F00A096C944}">
+    <comment ref="Y9" authorId="23" shapeId="0" xr:uid="{61C481F3-24C5-44D2-A4EE-6F00A096C944}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD9" authorId="4" shapeId="0" xr:uid="{A1052B11-CDA7-4355-85C8-B36DCDCBFA84}">
+    <comment ref="AD9" authorId="24" shapeId="0" xr:uid="{DBC8235E-71D5-47FF-8E3E-1916E90CD542}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J10" authorId="13" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
+    <comment ref="J10" authorId="25" shapeId="0" xr:uid="{3F53A83B-45F2-42F2-A9B5-E8DA49791B2C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V10" authorId="14" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
+    <comment ref="V10" authorId="26" shapeId="0" xr:uid="{7796FD16-CEF0-4762-99E2-2FEC910B3B1D}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y10" authorId="3" shapeId="0" xr:uid="{EBFD2544-76F8-46EB-966B-813ED3C87C82}">
+    <comment ref="Y10" authorId="27" shapeId="0" xr:uid="{EBFD2544-76F8-46EB-966B-813ED3C87C82}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD10" authorId="4" shapeId="0" xr:uid="{531A283A-AC70-4152-9BE6-43C54300A95C}">
+    <comment ref="AD10" authorId="28" shapeId="0" xr:uid="{F1B6EC79-122B-49DC-B8A4-162CF7AF8305}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J11" authorId="13" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
+    <comment ref="J11" authorId="29" shapeId="0" xr:uid="{A3E0CE26-0E37-40C5-8381-C747D12AA79B}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V11" authorId="14" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
+    <comment ref="V11" authorId="30" shapeId="0" xr:uid="{2919B58E-683F-4CF6-8A4B-E8E10D4282EE}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y11" authorId="3" shapeId="0" xr:uid="{CA845B26-4E91-41C7-9B80-A14104B366DD}">
+    <comment ref="Y11" authorId="31" shapeId="0" xr:uid="{CA845B26-4E91-41C7-9B80-A14104B366DD}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD11" authorId="4" shapeId="0" xr:uid="{27CA7D1E-600E-4B66-8951-581265F0DEE5}">
+    <comment ref="AD11" authorId="32" shapeId="0" xr:uid="{EA2FE5D6-4F0C-4646-AE08-D0F7B9C8C8B5}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="13" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
+    <comment ref="J12" authorId="33" shapeId="0" xr:uid="{2E79ADF3-A555-45DE-A94C-CB7982584A56}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V12" authorId="14" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
+    <comment ref="V12" authorId="34" shapeId="0" xr:uid="{EFA8EC15-6E5D-4B16-B46D-FA1A0144C7C4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y12" authorId="3" shapeId="0" xr:uid="{9119942B-138C-4E9B-896C-8017896C61D4}">
+    <comment ref="Y12" authorId="35" shapeId="0" xr:uid="{9119942B-138C-4E9B-896C-8017896C61D4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD12" authorId="4" shapeId="0" xr:uid="{1EDBEFA8-BB0A-4540-8BFB-23D5EA138441}">
+    <comment ref="AD12" authorId="36" shapeId="0" xr:uid="{7EF185CA-15B4-4C91-9245-26BC21024D49}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="13" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
+    <comment ref="J13" authorId="37" shapeId="0" xr:uid="{479DCC54-EFB5-4029-A8A1-A7B9AA4A2D71}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
-        </r>
       </text>
     </comment>
-    <comment ref="V13" authorId="14" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
+    <comment ref="V13" authorId="38" shapeId="0" xr:uid="{1394A269-74DE-46A3-AF1E-00ED042DEDC4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
-    <comment ref="Y13" authorId="3" shapeId="0" xr:uid="{9D71E412-A9DC-488B-91B8-61FE9E77AC39}">
+    <comment ref="Y13" authorId="39" shapeId="0" xr:uid="{9D71E412-A9DC-488B-91B8-61FE9E77AC39}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier 2010 "Relating ...": "g C bacteria (g C amphipods)^-1]". </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Foulquier 2010 Relating</t>
       </text>
     </comment>
-    <comment ref="AD13" authorId="4" shapeId="0" xr:uid="{AC533041-3EAD-4291-8203-F990E3DAA62A}">
+    <comment ref="AD13" authorId="40" shapeId="0" xr:uid="{4B3F8DBB-2689-47E0-BDF3-A01EAC67058C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Foulquier et al. (2010): of 0.35 / day </t>
-        </r>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
+Antwort:
+    19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
   </commentList>
@@ -1251,7 +498,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="198">
   <si>
     <t>variable_parameter</t>
   </si>
@@ -2259,9 +1506,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>difference between reference and +3deg C in the River zone after 3.5 years,</t>
-  </si>
-  <si>
     <t>mol / L / 3.5 years</t>
   </si>
   <si>
@@ -2338,18 +1582,50 @@
   </si>
   <si>
     <t>Alternatively , 0.1 as in Lindeman. Thats dry mass already.</t>
+  </si>
+  <si>
+    <t>COD difference in BOC between reference and no fauna in the mixing zone "M" zone after 3.5 years,</t>
+  </si>
+  <si>
+    <t>"   no fauna</t>
+  </si>
+  <si>
+    <t>1.5° increase in temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   " no fauna</t>
+  </si>
+  <si>
+    <t>3° increase in temperature</t>
+  </si>
+  <si>
+    <t>reference (ref.)</t>
+  </si>
+  <si>
+    <t>ref., lowest k1</t>
+  </si>
+  <si>
+    <t>ref., highest k1</t>
+  </si>
+  <si>
+    <t>ref., lowest yield</t>
+  </si>
+  <si>
+    <t>ref., highest yield</t>
+  </si>
+  <si>
+    <t>scenario</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.000000000E+00"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2469,12 +1745,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2524,7 +1794,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2557,9 +1827,8 @@
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2933,77 +2202,152 @@
   <threadedComment ref="J4" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{BC23984A-4BE5-DB42-8CB2-421621628373}">
     <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
   </threadedComment>
-  <threadedComment ref="X4" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{A973AB73-A4B2-DB42-8CE2-2E9D2BA6D327}">
+  <threadedComment ref="V4" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{A973AB73-A4B2-DB42-8CE2-2E9D2BA6D327}">
     <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
   </threadedComment>
-  <threadedComment ref="AB4" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
+  <threadedComment ref="Y4" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
     <text>Foulquier 2010 Relating</text>
   </threadedComment>
-  <threadedComment ref="AG4" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8543-91DC-DFD968583D4B}">
+  <threadedComment ref="AD4" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8543-91DC-DFD968583D4B}">
     <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
   </threadedComment>
-  <threadedComment ref="AG4" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-944D-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8543-91DC-DFD968583D4B}">
+  <threadedComment ref="AD4" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-944D-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8543-91DC-DFD968583D4B}">
     <text>19.6.25 geändert, siehe SI</text>
   </threadedComment>
   <threadedComment ref="J5" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}">
     <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
   </threadedComment>
-  <threadedComment ref="X5" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{8B1BECD1-664B-894E-902F-58308D659DA9}">
+  <threadedComment ref="V5" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{8B1BECD1-664B-894E-902F-58308D659DA9}">
     <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
   </threadedComment>
-  <threadedComment ref="AB5" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
+  <threadedComment ref="Y5" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B842-B3B1-49218DCB8340}">
     <text>Foulquier 2010 Relating</text>
   </threadedComment>
-  <threadedComment ref="AG5" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{009AF6C5-B9AC-7541-9E56-015D22C54F6F}">
+  <threadedComment ref="AD5" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8544-91DC-DFD968583D4B}">
     <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD5" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-944E-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8544-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
   </threadedComment>
   <threadedComment ref="J6" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
     <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
   </threadedComment>
-  <threadedComment ref="X6" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
+  <threadedComment ref="V6" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
     <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
   </threadedComment>
-  <threadedComment ref="AB6" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
+  <threadedComment ref="Y6" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B843-B3B1-49218DCB8340}">
     <text>Foulquier 2010 Relating</text>
   </threadedComment>
-  <threadedComment ref="AG6" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B40E02FA-A395-684A-865E-E43D81BF9EF7}">
+  <threadedComment ref="AD6" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8545-91DC-DFD968583D4B}">
     <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD6" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-944F-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8545-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
   </threadedComment>
   <threadedComment ref="J7" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
     <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
   </threadedComment>
-  <threadedComment ref="X7" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
+  <threadedComment ref="V7" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
     <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
   </threadedComment>
-  <threadedComment ref="AB7" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
+  <threadedComment ref="Y7" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B844-B3B1-49218DCB8340}">
     <text>Foulquier 2010 Relating</text>
   </threadedComment>
-  <threadedComment ref="AG7" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{507182A8-A16E-3B46-A78B-C475F7E79FFC}">
+  <threadedComment ref="AD7" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8546-91DC-DFD968583D4B}">
     <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD7" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9450-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8546-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
   </threadedComment>
   <threadedComment ref="J8" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
     <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
   </threadedComment>
-  <threadedComment ref="X8" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
+  <threadedComment ref="V8" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
     <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
   </threadedComment>
-  <threadedComment ref="AB8" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
+  <threadedComment ref="Y8" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B845-B3B1-49218DCB8340}">
     <text>Foulquier 2010 Relating</text>
   </threadedComment>
-  <threadedComment ref="AG8" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{C8D487C4-854D-254E-A24C-BB3F3463062E}">
+  <threadedComment ref="AD8" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8547-91DC-DFD968583D4B}">
     <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD8" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9451-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8547-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
   </threadedComment>
   <threadedComment ref="J9" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
     <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
   </threadedComment>
-  <threadedComment ref="X9" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
+  <threadedComment ref="V9" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
     <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
   </threadedComment>
-  <threadedComment ref="AB9" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
+  <threadedComment ref="Y9" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B846-B3B1-49218DCB8340}">
     <text>Foulquier 2010 Relating</text>
   </threadedComment>
-  <threadedComment ref="AG9" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}">
+  <threadedComment ref="AD9" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8548-91DC-DFD968583D4B}">
     <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD9" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9452-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8548-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
+  </threadedComment>
+  <threadedComment ref="J10" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E68EDC32-0C11-F250-BC92-6599E44DEE2B}">
+    <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
+  </threadedComment>
+  <threadedComment ref="V10" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{03DDDF21-1FDE-1A45-92CB-02C9D1E67681}">
+    <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
+  </threadedComment>
+  <threadedComment ref="Y10" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B847-B3B1-49218DCB8340}">
+    <text>Foulquier 2010 Relating</text>
+  </threadedComment>
+  <threadedComment ref="AD10" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-8549-91DC-DFD968583D4B}">
+    <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD10" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9453-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-8549-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
+  </threadedComment>
+  <threadedComment ref="J11" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E68EDC32-0C11-F251-BC92-6599E44DEE2B}">
+    <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
+  </threadedComment>
+  <threadedComment ref="V11" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{03DDDF21-1FDE-1A46-92CB-02C9D1E67681}">
+    <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
+  </threadedComment>
+  <threadedComment ref="Y11" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B848-B3B1-49218DCB8340}">
+    <text>Foulquier 2010 Relating</text>
+  </threadedComment>
+  <threadedComment ref="AD11" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-854A-91DC-DFD968583D4B}">
+    <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD11" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9454-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-854A-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
+  </threadedComment>
+  <threadedComment ref="J12" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E68EDC32-0C11-F252-BC92-6599E44DEE2B}">
+    <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
+  </threadedComment>
+  <threadedComment ref="V12" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{03DDDF21-1FDE-1A47-92CB-02C9D1E67681}">
+    <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
+  </threadedComment>
+  <threadedComment ref="Y12" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B849-B3B1-49218DCB8340}">
+    <text>Foulquier 2010 Relating</text>
+  </threadedComment>
+  <threadedComment ref="AD12" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-854B-91DC-DFD968583D4B}">
+    <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD12" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9455-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-854B-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
+  </threadedComment>
+  <threadedComment ref="J13" dT="2025-06-02T13:55:05.15" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{E68EDC32-0C11-F253-BC92-6599E44DEE2B}">
+    <text>7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</text>
+  </threadedComment>
+  <threadedComment ref="V13" dT="2025-06-15T11:12:50.61" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{03DDDF21-1FDE-1A48-92CB-02C9D1E67681}">
+    <text>average of Di Lorenzo, Navel, Mermillod-Blondin</text>
+  </threadedComment>
+  <threadedComment ref="Y13" dT="2025-06-07T18:46:12.83" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{B2EEDDFE-EFB6-B84A-B3B1-49218DCB8340}">
+    <text>Foulquier 2010 Relating</text>
+  </threadedComment>
+  <threadedComment ref="AD13" dT="2025-06-15T10:42:48.50" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D83D8722-287D-854C-91DC-DFD968583D4B}">
+    <text>Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</text>
+  </threadedComment>
+  <threadedComment ref="AD13" dT="2025-06-20T08:24:23.10" personId="{FE8B650B-F8E4-BC41-8B83-E1DC95C47930}" id="{D5A6F296-99E3-9456-9E17-1BB8F5BD2616}" parentId="{D83D8722-287D-854C-91DC-DFD968583D4B}">
+    <text>19.6.25 geändert, siehe SI</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3011,15 +2355,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}">
   <dimension ref="A1:AI15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.19921875" customWidth="1"/>
-    <col min="13" max="13" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" customWidth="1"/>
+    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -3033,22 +2377,22 @@
         <v>47</v>
       </c>
       <c r="F1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" t="s">
         <v>177</v>
       </c>
-      <c r="G1" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>178</v>
-      </c>
-      <c r="L1" t="s">
-        <v>179</v>
       </c>
       <c r="M1" t="s">
         <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O1" t="s">
         <v>5</v>
@@ -3057,34 +2401,37 @@
         <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="W1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y1" t="s">
         <v>186</v>
       </c>
-      <c r="Y1" t="s">
-        <v>187</v>
-      </c>
       <c r="Z1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AG1" t="s">
         <v>181</v>
       </c>
-      <c r="AA1" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD1" t="s">
+      <c r="AI1" t="s">
         <v>184</v>
       </c>
-      <c r="AE1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="2" spans="1:35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
@@ -3109,7 +2456,7 @@
     </row>
     <row r="3" spans="1:35">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -3126,8 +2473,8 @@
       <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>173</v>
+      <c r="G3" t="s">
+        <v>172</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -3215,6 +2562,9 @@
       </c>
     </row>
     <row r="4" spans="1:35">
+      <c r="A4" t="s">
+        <v>192</v>
+      </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -3306,8 +2656,9 @@
       <c r="AC4">
         <v>0</v>
       </c>
-      <c r="AD4" s="23">
-        <v>0.35</v>
+      <c r="AD4" s="22">
+        <f>X4/100</f>
+        <v>0.1032</v>
       </c>
       <c r="AE4">
         <f>0.0001</f>
@@ -3328,6 +2679,9 @@
       </c>
     </row>
     <row r="5" spans="1:35">
+      <c r="A5" t="s">
+        <v>188</v>
+      </c>
       <c r="B5">
         <v>2</v>
       </c>
@@ -3419,15 +2773,16 @@
       <c r="AC5">
         <v>0</v>
       </c>
-      <c r="AD5" s="23">
-        <v>0.35</v>
+      <c r="AD5" s="22">
+        <f t="shared" ref="AD5:AD13" si="7">X5/100</f>
+        <v>0.1032</v>
       </c>
       <c r="AE5">
-        <f t="shared" ref="AE5:AF13" si="7">0.0001</f>
+        <f t="shared" ref="AE5:AF13" si="8">0.0001</f>
         <v>1E-4</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG5">
@@ -3441,6 +2796,9 @@
       </c>
     </row>
     <row r="6" spans="1:35">
+      <c r="A6" t="s">
+        <v>189</v>
+      </c>
       <c r="B6">
         <v>3</v>
       </c>
@@ -3470,14 +2828,14 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K9" si="8">J6/1000</f>
+        <f t="shared" ref="K6:K9" si="9">J6/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L6" s="4">
         <v>10</v>
       </c>
       <c r="M6">
-        <f t="shared" ref="M6" si="9">L6*J6</f>
+        <f t="shared" ref="M6" si="10">L6*J6</f>
         <v>10.752025361042621</v>
       </c>
       <c r="N6">
@@ -3503,7 +2861,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U9" si="10">4.3 /1000000 *1.07</f>
+        <f t="shared" ref="U6:U9" si="11">4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V6">
@@ -3532,15 +2890,16 @@
       <c r="AC6">
         <v>0</v>
       </c>
-      <c r="AD6" s="23">
-        <v>0.35</v>
+      <c r="AD6" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG6">
@@ -3554,6 +2913,9 @@
       </c>
     </row>
     <row r="7" spans="1:35">
+      <c r="A7" t="s">
+        <v>190</v>
+      </c>
       <c r="B7">
         <v>4</v>
       </c>
@@ -3583,7 +2945,7 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L7" s="4">
@@ -3616,7 +2978,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V7">
@@ -3645,15 +3007,16 @@
       <c r="AC7">
         <v>0</v>
       </c>
-      <c r="AD7" s="23">
-        <v>0.35</v>
+      <c r="AD7" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG7">
@@ -3667,6 +3030,9 @@
       </c>
     </row>
     <row r="8" spans="1:35">
+      <c r="A8" t="s">
+        <v>191</v>
+      </c>
       <c r="B8">
         <v>5</v>
       </c>
@@ -3696,14 +3062,14 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L8" s="4">
         <v>10</v>
       </c>
       <c r="M8">
-        <f t="shared" ref="M8" si="11">L8*J8</f>
+        <f t="shared" ref="M8" si="12">L8*J8</f>
         <v>10.752025361042621</v>
       </c>
       <c r="N8">
@@ -3729,7 +3095,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V8">
@@ -3758,15 +3124,16 @@
       <c r="AC8">
         <v>0</v>
       </c>
-      <c r="AD8" s="23">
-        <v>0.35</v>
+      <c r="AD8" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG8">
@@ -3780,6 +3147,9 @@
       </c>
     </row>
     <row r="9" spans="1:35">
+      <c r="A9" t="s">
+        <v>190</v>
+      </c>
       <c r="B9">
         <v>6</v>
       </c>
@@ -3809,7 +3179,7 @@
         <v>1.0752025361042621</v>
       </c>
       <c r="K9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L9" s="4">
@@ -3842,7 +3212,7 @@
         <v>0.47258333333333336</v>
       </c>
       <c r="U9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V9">
@@ -3871,15 +3241,16 @@
       <c r="AC9">
         <v>0</v>
       </c>
-      <c r="AD9" s="23">
-        <v>0.35</v>
+      <c r="AD9" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG9">
@@ -3893,6 +3264,9 @@
       </c>
     </row>
     <row r="10" spans="1:35">
+      <c r="A10" t="s">
+        <v>193</v>
+      </c>
       <c r="B10">
         <v>7</v>
       </c>
@@ -3918,11 +3292,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J10">
-        <f t="shared" ref="J10:J11" si="12">I10*7.5</f>
+        <f t="shared" ref="J10:J11" si="13">I10*7.5</f>
         <v>1.0752025361042621</v>
       </c>
       <c r="K10">
-        <f t="shared" ref="K10:K11" si="13">J10/1000</f>
+        <f t="shared" ref="K10:K11" si="14">J10/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L10" s="4">
@@ -3951,11 +3325,11 @@
         <v>30</v>
       </c>
       <c r="T10">
-        <f t="shared" ref="T10:T11" si="14">10.6/12*1.07/2</f>
+        <f t="shared" ref="T10:T11" si="15">10.6/12*1.07/2</f>
         <v>0.47258333333333336</v>
       </c>
       <c r="U10">
-        <f t="shared" ref="U10:U13" si="15">4.3 /1000000 *1.07</f>
+        <f t="shared" ref="U10:U13" si="16">4.3 /1000000 *1.07</f>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V10">
@@ -3984,15 +3358,16 @@
       <c r="AC10">
         <v>0</v>
       </c>
-      <c r="AD10" s="23">
-        <v>0.35</v>
+      <c r="AD10" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG10">
@@ -4006,6 +3381,9 @@
       </c>
     </row>
     <row r="11" spans="1:35">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
       <c r="B11">
         <v>8</v>
       </c>
@@ -4031,11 +3409,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L11" s="4">
@@ -4046,7 +3424,7 @@
         <v>10.752025361042621</v>
       </c>
       <c r="N11" s="21">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -4064,11 +3442,11 @@
         <v>30</v>
       </c>
       <c r="T11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.47258333333333336</v>
       </c>
       <c r="U11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V11">
@@ -4097,15 +3475,16 @@
       <c r="AC11">
         <v>0</v>
       </c>
-      <c r="AD11" s="23">
-        <v>0.35</v>
+      <c r="AD11" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG11">
@@ -4119,6 +3498,9 @@
       </c>
     </row>
     <row r="12" spans="1:35">
+      <c r="A12" t="s">
+        <v>195</v>
+      </c>
       <c r="B12">
         <v>9</v>
       </c>
@@ -4144,11 +3526,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J12">
-        <f t="shared" ref="J12:J13" si="16">I12*7.5</f>
+        <f t="shared" ref="J12:J13" si="17">I12*7.5</f>
         <v>1.0752025361042621</v>
       </c>
       <c r="K12">
-        <f t="shared" ref="K12:K13" si="17">J12/1000</f>
+        <f t="shared" ref="K12:K13" si="18">J12/1000</f>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L12" s="4">
@@ -4180,7 +3562,7 @@
         <v>1E-3</v>
       </c>
       <c r="U12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V12">
@@ -4209,15 +3591,16 @@
       <c r="AC12">
         <v>0</v>
       </c>
-      <c r="AD12" s="23">
-        <v>0.35</v>
+      <c r="AD12" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG12">
@@ -4231,6 +3614,9 @@
       </c>
     </row>
     <row r="13" spans="1:35">
+      <c r="A13" t="s">
+        <v>196</v>
+      </c>
       <c r="B13">
         <v>10</v>
       </c>
@@ -4256,11 +3642,11 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="J13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.0752025361042621</v>
       </c>
       <c r="K13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.075202536104262E-3</v>
       </c>
       <c r="L13" s="4">
@@ -4292,7 +3678,7 @@
         <v>0.8</v>
       </c>
       <c r="U13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.6009999999999997E-6</v>
       </c>
       <c r="V13">
@@ -4321,15 +3707,16 @@
       <c r="AC13">
         <v>0</v>
       </c>
-      <c r="AD13" s="23">
-        <v>0.35</v>
+      <c r="AD13" s="22">
+        <f t="shared" si="7"/>
+        <v>0.1032</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1E-4</v>
       </c>
       <c r="AG13">
@@ -4343,10 +3730,10 @@
       </c>
     </row>
     <row r="14" spans="1:35">
-      <c r="AD14" s="23"/>
+      <c r="AD14" s="22"/>
     </row>
     <row r="15" spans="1:35">
-      <c r="AD15" s="24"/>
+      <c r="AD15" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AI3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}"/>
@@ -4359,10 +3746,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92644CC1-E167-AE40-81F2-8D9D4BC8EB36}">
   <dimension ref="B1:U139"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:21">
@@ -5252,7 +4639,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="108" spans="4:14">
+    <row r="108" spans="4:14" ht="20">
       <c r="D108">
         <v>14.9</v>
       </c>
@@ -5421,33 +4808,33 @@
         <v>155</v>
       </c>
     </row>
-    <row r="130" spans="4:6" ht="198">
+    <row r="130" spans="4:6" ht="210">
       <c r="D130" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="4:6">
       <c r="D131">
-        <f xml:space="preserve"> 1.6*10^-5</f>
-        <v>1.6000000000000003E-5</v>
+        <f xml:space="preserve"> 7.3*10^-5</f>
+        <v>7.2999999999999999E-5</v>
       </c>
       <c r="E131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F131" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
     </row>
     <row r="132" spans="4:6">
       <c r="D132">
         <f>D131/3.5</f>
-        <v>4.5714285714285719E-6</v>
+        <v>2.0857142857142857E-5</v>
       </c>
       <c r="E132" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="133" spans="4:6">
@@ -5476,13 +4863,13 @@
     <row r="135" spans="4:6">
       <c r="D135">
         <f>D134*D132</f>
-        <v>2880000000000.0005</v>
+        <v>13140000000000</v>
       </c>
       <c r="E135" t="s">
+        <v>163</v>
+      </c>
+      <c r="F135" t="s">
         <v>164</v>
-      </c>
-      <c r="F135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="4:6">
@@ -5491,46 +4878,46 @@
         <v>227</v>
       </c>
       <c r="E136" t="s">
+        <v>166</v>
+      </c>
+      <c r="F136" t="s">
         <v>167</v>
-      </c>
-      <c r="F136" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="137" spans="4:6">
       <c r="D137">
         <f>D135*D136</f>
-        <v>653760000000000.13</v>
+        <v>2982780000000000</v>
       </c>
       <c r="E137" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F137" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="138" spans="4:6">
       <c r="D138">
         <f>D137/1000</f>
-        <v>653760000000.00012</v>
+        <v>2982780000000</v>
       </c>
       <c r="E138" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F138" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="139" spans="4:6">
       <c r="D139">
         <f>D138/1000</f>
-        <v>653760000.00000012</v>
+        <v>2982780000</v>
       </c>
       <c r="E139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
